--- a/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1770,6 +1770,341 @@
       <c r="Q16" t="inlineStr">
         <is>
           <t>output/pdfs/WA/134572006/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12/31/2025</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>04.0001 Condominium Homeowners</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>18.800%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4.900%</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>563934</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>11751</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>11487151</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>6.800%</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.500%</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>LBPM-134619371</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>02/21/2026</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-3.100%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-3.300%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-273240</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>36921</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>8303864</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>-37.500%</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>LBPM-134745236</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>12/13/2025</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>5324</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>22469034</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>GMMX-134659152</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134659152/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>22469034</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>GMMX-134645542</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134645542/filing_summary.pdf</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>03/18/2025</t>
+          <t>07/24/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1296,12 +1296,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-13.700%</t>
+          <t>-2.900%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-109613</t>
+          <t>-20025</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1309,17 +1309,17 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>800092</t>
+          <t>690507</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-32.200%</t>
+          <t>-5.700%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ALSE-134416811</t>
+          <t>ALSE-134500694</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134416811/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134500694/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>03/18/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1381,30 +1381,30 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-2.400%</t>
+          <t>-13.700%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-313375</t>
+          <t>-109613</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>8451</v>
+        <v>472</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13057296</t>
+          <t>800092</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.700%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>-32.200%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>ALSE-134597553</t>
+          <t>ALSE-134416811</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134597553/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134416811/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>-2.400%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-1425594</t>
+          <t>-313375</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>27336</v>
+        <v>8451</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>43199831</t>
+          <t>13057296</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-9.200%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>ALSE-134684477</t>
+          <t>ALSE-134597553</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134684477/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134597553/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1551,20 +1551,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1425594</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>27336</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6895556</t>
+          <t>43199831</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-9.200%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>ALSE-134489925</t>
+          <t>ALSE-134684477</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134489925/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134684477/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1611,55 +1611,55 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>01/19/2026</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>675285</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>6107</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5681808</t>
+          <t>6895556</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ALSE-134517504</t>
+          <t>ALSE-134489925</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134517504/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134489925/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08/04/2025</t>
+          <t>01/19/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1711,40 +1711,40 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.900%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.900%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>675285</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>123621</v>
+        <v>6107</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>233084721</t>
+          <t>5681808</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4.200%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-3.700%</t>
+          <t>5.600%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>ALSE-134572006</t>
+          <t>ALSE-134517504</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134572006/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134517504/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12/31/2025</t>
+          <t>08/04/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1796,40 +1796,40 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>563934</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>11751</v>
+        <v>123621</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11487151</t>
+          <t>233084721</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6.800%</t>
+          <t>4.200%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>-3.700%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>LBPM-134619371</t>
+          <t>ALSE-134572006</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134572006/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>12/31/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1881,40 +1881,40 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-3.100%</t>
+          <t>18.800%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>4.900%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-273240</t>
+          <t>563934</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>36921</v>
+        <v>11751</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>8303864</t>
+          <t>11487151</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.800%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-37.500%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>LBPM-134745236</t>
+          <t>LBPM-134619371</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1951,45 +1951,45 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.100%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-273240</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5324</v>
+        <v>36921</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>22469034</t>
+          <t>8303864</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-37.500%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>GMMX-134659152</t>
+          <t>LBPM-134745236</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134659152/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2034,6 +2034,11 @@
           <t>WA</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>12/13/2025</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>Encompass Indemnity Company</t>
@@ -2065,44 +2070,124 @@
         </is>
       </c>
       <c r="I20" t="n">
+        <v>5324</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>22469034</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>GMMX-134659152</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134659152/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>22469034</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>GMMX-134645542</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>2025-09-03</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>output/pdfs/WA/134645542/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,50 +511,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>08/01/2025</t>
+          <t>02/03/2025</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9.600%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>23.900%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3367834</t>
+          <t>55166401</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>17873</v>
+        <v>200145</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>14091908</t>
+          <t>606224182</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>27.700%</t>
+          <t>48.000%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.100%</t>
+          <t>-1.000%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -564,7 +569,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>SFMA-134422784</t>
+          <t>ALSE-134206307</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -574,12 +579,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134422784/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134206307/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -591,55 +596,55 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>17.900%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.500%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2752700</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2090</v>
+        <v>13118</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1077172</t>
+          <t>23936525</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>24.800%</t>
+          <t>13.200%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-17.900%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -649,7 +654,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>GECC-134628136</t>
+          <t>ALSE-134326701</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -659,12 +664,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134326701/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -676,55 +681,55 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2542799</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>946</v>
+        <v>17045</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>493777</t>
+          <t>28570771</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>24.400%</t>
+          <t>10.500%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-17.500%</t>
+          <t>5.500%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -734,7 +739,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>GECC-134628136</t>
+          <t>ALSE-134327525</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -744,12 +749,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134327525/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -761,55 +766,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.400%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.900%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3779468</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>468</v>
+        <v>43927</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>313322</t>
+          <t>77131999</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>22.000%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-15.200%</t>
+          <t>1.900%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -819,7 +824,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>GECC-134629877</t>
+          <t>ALSE-134328097</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -829,12 +834,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629877/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134328097/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -846,55 +851,55 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>27.100%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>20.900%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46373640</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>6838</v>
+        <v>118778</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3570611</t>
+          <t>221883447</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>22.700%</t>
+          <t>21.700%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-18.900%</t>
+          <t>17.900%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -904,7 +909,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>GECC-134629950</t>
+          <t>ALSE-134345731</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -914,12 +919,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134345731/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -931,12 +936,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>03/18/2025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -946,7 +951,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -956,30 +961,30 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-13.700%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-109613</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1090</v>
+        <v>472</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>851643</t>
+          <t>800092</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>22.200%</t>
+          <t>13.700%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-19.000%</t>
+          <t>-32.200%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>GECC-134629950</t>
+          <t>ALSE-134416811</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -999,12 +1004,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134416811/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1016,12 +1021,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1031,7 +1036,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1050,21 +1055,21 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>268980</t>
+          <t>541730713</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>19.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-15.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1074,7 +1079,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>GECC-134629950</t>
+          <t>ALSE-134489276</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1084,12 +1089,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134489276/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1111,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1116,7 +1121,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1139,7 +1144,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>541730713</t>
+          <t>6895556</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1159,7 +1164,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ALSE-134489276</t>
+          <t>ALSE-134489925</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1174,7 +1179,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134489276/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134489925/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1191,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>07/24/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1206,35 +1211,35 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.900%</t>
+          <t>-2.900%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1129791</t>
+          <t>-20025</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3980</v>
+        <v>472</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16373783</t>
+          <t>690507</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>12.600%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.700%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1244,7 +1249,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ALSE-134538132</t>
+          <t>ALSE-134500694</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1254,12 +1259,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134538132/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134500694/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1271,55 +1276,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>07/24/2025</t>
+          <t>01/19/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.900%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.900%</t>
+          <t>11.900%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-20025</t>
+          <t>675285</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>472</v>
+        <v>6107</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>690507</t>
+          <t>5681808</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.800%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-5.700%</t>
+          <t>5.600%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1329,7 +1334,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ALSE-134500694</t>
+          <t>ALSE-134517504</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1339,12 +1344,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134500694/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134517504/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1361,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>03/18/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1376,35 +1381,35 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.900%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-13.700%</t>
+          <t>6.900%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-109613</t>
+          <t>1129791</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>472</v>
+        <v>3980</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>800092</t>
+          <t>16373783</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>12.600%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-32.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1414,7 +1419,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>ALSE-134416811</t>
+          <t>ALSE-134538132</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1424,12 +1429,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134416811/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134538132/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1441,22 +1446,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>08/04/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1466,30 +1471,30 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-313375</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>8451</v>
+        <v>123621</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13057296</t>
+          <t>233084721</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.200%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>-3.700%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1499,7 +1504,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>ALSE-134597553</t>
+          <t>ALSE-134572006</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1509,12 +1514,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134597553/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134572006/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1531,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1551,20 +1556,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>-2.400%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1425594</t>
+          <t>-313375</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>27336</v>
+        <v>8451</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>43199831</t>
+          <t>13057296</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1574,7 +1579,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-9.200%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1584,7 +1589,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>ALSE-134684477</t>
+          <t>ALSE-134597553</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1594,12 +1599,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134684477/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134597553/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1616,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1626,7 +1631,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1636,20 +1641,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1425594</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>27336</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6895556</t>
+          <t>43199831</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1659,7 +1664,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-9.200%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1669,7 +1674,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ALSE-134489925</t>
+          <t>ALSE-134684477</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1679,12 +1684,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134489925/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134684477/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1696,55 +1701,55 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01/19/2026</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>11.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>675285</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6107</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5681808</t>
+          <t>18275978</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1754,7 +1759,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>ALSE-134517504</t>
+          <t>ALSE-134214686</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1764,12 +1769,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134517504/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134214686/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1779,24 +1784,19 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>08/04/2025</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1815,21 +1815,21 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>123621</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>233084721</t>
+          <t>22469034</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-3.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>ALSE-134572006</t>
+          <t>GMMX-134645542</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134572006/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134645542/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1866,55 +1866,55 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12/31/2025</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>18.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>563934</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>11751</v>
+        <v>5324</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>11487151</t>
+          <t>22469034</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>LBPM-134619371</t>
+          <t>GMMX-134659152</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134659152/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1951,55 +1951,55 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-3.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-273240</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>36921</v>
+        <v>2090</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8303864</t>
+          <t>1077172</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>24.800%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-37.500%</t>
+          <t>-17.900%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>LBPM-134745236</t>
+          <t>GECC-134628136</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2036,12 +2036,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2070,21 +2070,21 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>5324</v>
+        <v>946</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>22469034</t>
+          <t>493777</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>24.400%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-17.500%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>GMMX-134659152</t>
+          <t>GECC-134628136</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2104,12 +2104,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134659152/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2119,9 +2119,14 @@
           <t>WA</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>09/18/2025</t>
+        </is>
+      </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2131,65 +2136,1240 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>468</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>313322</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>22.000%</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-15.200%</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>GECC-134629877</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134629877/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>09/18/2025</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GEICO Advantage Insurance Company</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>6838</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>3570611</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>22.700%</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-18.900%</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>GECC-134629950</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>09/18/2025</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GEICO Choice Insurance Company</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1090</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>851643</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>22.200%</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-19.000%</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>GECC-134629950</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>09/18/2025</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GEICO Secure Insurance Company</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>220</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>268980</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>19.400%</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-15.800%</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>GECC-134629950</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>22469034</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
+      <c r="I25" t="n">
+        <v>136399</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>202923596</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>8.800%</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-8.200%</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>GMMX-134645542</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>PRGS-134191751</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-09-03</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>output/pdfs/WA/134645542/filing_summary.pdf</t>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>314349</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>306405692</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>11.300%</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-8.500%</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>PRGS-134191751</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>03/16/2025</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>10.200%</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>9.900%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>986227</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>21127</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>9923754</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>13.700%</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>LBPM-134220016</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134220016/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>12/31/2025</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>04.0001 Condominium Homeowners</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>18.800%</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>4.900%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>563934</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>11751</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>11487151</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>6.800%</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0.500%</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>LBPM-134619371</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>02/21/2026</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-3.100%</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-3.300%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-273240</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>36921</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>8303864</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-37.500%</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>LBPM-134745236</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>12/15/2025</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>21.500%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>10650679</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>59070</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>49543045</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>22.800%</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>SFMA-134315085</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134315085/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>93.700%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2706726</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>8405</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2888541</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>108.400%</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>31.400%</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>SFMA-134315091</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134315091/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08/01/2025</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>04.0002 Mobile Homeowners</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>23.900%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>3367834</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>17873</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>14091908</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>27.700%</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>5.100%</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>SFMA-134422784</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134422784/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>02/08/2025</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>31.500%</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>21.100%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>10657508</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>39456</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>50509518</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>33.400%</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>TRVD-G134262689</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>02/08/2025</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>31.500%</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>21.400%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>636936</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>2461</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2976338</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>32.600%</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>TRVD-G134262689</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>03/30/2025</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>2483</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>4953073</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>TRVD-G134336116</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134358134/filing_summary.pdf</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:R85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,6 +502,11 @@
           <t>source_pdf</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>validation_tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -511,7 +516,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>02/03/2025</t>
+          <t>01/15/2024</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -531,35 +536,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9.600%</t>
+          <t>20.700%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>9.100%</t>
+          <t>20.400%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>55166401</t>
+          <t>99983292</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>200145</v>
+        <v>194444</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>606224182</t>
+          <t>490114177</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>48.000%</t>
+          <t>31.300%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-1.000%</t>
+          <t>5.700%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -569,7 +574,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ALSE-134206307</t>
+          <t>ALSE-133789684</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -579,12 +584,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134206307/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133789684/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -596,7 +606,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>02/26/2024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -616,35 +626,35 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17.900%</t>
+          <t>8.700%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>11.500%</t>
+          <t>3.200%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2752700</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>13118</v>
+        <v>14343</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>23936525</t>
+          <t>25452380</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>13.200%</t>
+          <t>5.400%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>1.700%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -654,7 +664,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ALSE-134326701</t>
+          <t>ALSE-133897373</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -664,12 +674,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134326701/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133897373/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -681,12 +696,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>02/26/2024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -701,35 +716,35 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.900%</t>
+          <t>6.600%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2542799</t>
+          <t>5108310</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>17045</v>
+        <v>48054</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28570771</t>
+          <t>77398640</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>10.500%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5.500%</t>
+          <t>2.400%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -739,7 +754,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ALSE-134327525</t>
+          <t>ALSE-133897486</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -749,12 +764,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134327525/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133897486/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -766,12 +786,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>02/26/2024</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -786,35 +806,35 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>11.400%</t>
+          <t>10.200%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.900%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3779468</t>
+          <t>1408003</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>43927</v>
+        <v>18389</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>77131999</t>
+          <t>29333392</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8.900%</t>
+          <t>8.800%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1.900%</t>
+          <t>2.600%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -824,7 +844,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ALSE-134328097</t>
+          <t>ALSE-133902389</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -834,12 +854,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134328097/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133902389/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -851,7 +876,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>03/11/2024</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -871,35 +896,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>27.100%</t>
+          <t>65.500%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20.900%</t>
+          <t>39.900%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>46373640</t>
+          <t>56647288</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>118778</v>
+        <v>106686</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>221883447</t>
+          <t>141973154</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>21.700%</t>
+          <t>109.800%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>17.900%</t>
+          <t>16.700%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -909,7 +934,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ALSE-134345731</t>
+          <t>ALSE-133920075</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -919,12 +944,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134345731/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133920075/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -936,12 +966,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>03/18/2025</t>
+          <t>04/15/2024</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -954,37 +984,32 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-13.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-109613</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>472</v>
+        <v>194444</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>800092</t>
+          <t>602924930</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>84.600%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-32.200%</t>
+          <t>-3.400%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -994,7 +1019,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ALSE-134416811</t>
+          <t>ALSE-133975008</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1004,12 +1029,17 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134416811/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133975008/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1051,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>08/12/2024</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1059,7 +1089,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>541730713</t>
+          <t>413455792</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1079,7 +1109,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ALSE-134489276</t>
+          <t>ALSE-134098985</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1089,12 +1119,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134489276/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134098985/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1141,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>08/12/2024</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1144,7 +1179,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6895556</t>
+          <t>6928058</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1164,7 +1199,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ALSE-134489925</t>
+          <t>ALSE-134099016</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1174,12 +1209,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134489925/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134099016/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1191,55 +1231,55 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>07/24/2025</t>
+          <t>03/24/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.900%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-20025</t>
+          <t>926592</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>472</v>
+        <v>9705</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>690507</t>
+          <t>11699459</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.800%</t>
+          <t>10.400%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-5.700%</t>
+          <t>2.500%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1249,7 +1289,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ALSE-134500694</t>
+          <t>ALSE-134119095</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1259,12 +1299,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134500694/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134119095/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
         </is>
       </c>
     </row>
@@ -1276,55 +1321,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>01/19/2026</t>
+          <t>02/17/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>11.900%</t>
+          <t>16.500%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>11.900%</t>
+          <t>13.400%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>675285</t>
+          <t>2392710</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6107</v>
+        <v>5557</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5681808</t>
+          <t>17856043</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>24.800%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1334,7 +1379,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ALSE-134517504</t>
+          <t>ALSE-134135043</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1344,12 +1389,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134517504/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134135043/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1411,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>09/23/2024</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1381,30 +1431,30 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6.900%</t>
+          <t>16.400%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6.900%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1129791</t>
+          <t>1880630</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3980</v>
+        <v>26873</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16373783</t>
+          <t>62687682</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>12.600%</t>
+          <t>8.200%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1419,7 +1469,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>ALSE-134538132</t>
+          <t>ALSE-134138722</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1429,12 +1479,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134538132/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134138722/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1446,55 +1501,55 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>08/04/2025</t>
+          <t>09/23/2024</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>20.900%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.800%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2874136</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>123621</v>
+        <v>10248</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>233084721</t>
+          <t>26612374</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4.200%</t>
+          <t>17.800%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-3.700%</t>
+          <t>0.800%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1504,7 +1559,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>ALSE-134572006</t>
+          <t>ALSE-134142123</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1514,12 +1569,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134572006/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134142123/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1591,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>02/03/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1551,35 +1611,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.600%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.400%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-313375</t>
+          <t>55166401</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>8451</v>
+        <v>200145</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13057296</t>
+          <t>606224182</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>48.000%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>-1.000%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1589,7 +1649,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>ALSE-134597553</t>
+          <t>ALSE-134206307</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1599,12 +1659,17 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134597553/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134206307/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1681,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>11/25/2024</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1641,20 +1706,20 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1425594</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>27336</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>43199831</t>
+          <t>61240239</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1664,7 +1729,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-9.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1674,7 +1739,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ALSE-134684477</t>
+          <t>ALSE-134214513</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1684,12 +1749,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134684477/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134214513/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1771,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01/06/2025</t>
+          <t>11/25/2024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1739,7 +1809,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18275978</t>
+          <t>24887220</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1759,7 +1829,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>ALSE-134214686</t>
+          <t>ALSE-134214513</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1774,7 +1844,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134214686/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134214513/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1784,9 +1859,14 @@
           <t>WA</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>11/25/2024</t>
+        </is>
+      </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1819,7 +1899,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22469034</t>
+          <t>15804620</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1839,7 +1919,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>GMMX-134645542</t>
+          <t>ALSE-134214513</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1849,12 +1929,17 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134645542/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134214513/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
         </is>
       </c>
     </row>
@@ -1866,55 +1951,55 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>17.900%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.500%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2752700</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5324</v>
+        <v>13118</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>22469034</t>
+          <t>23936525</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.200%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1924,7 +2009,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>GMMX-134659152</t>
+          <t>ALSE-134326701</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1934,12 +2019,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134659152/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134326701/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -1951,55 +2041,55 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2542799</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2090</v>
+        <v>17045</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1077172</t>
+          <t>28570771</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>24.800%</t>
+          <t>10.500%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-17.900%</t>
+          <t>5.500%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2009,7 +2099,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>GECC-134628136</t>
+          <t>ALSE-134327525</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2019,12 +2109,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134327525/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2036,55 +2131,55 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.400%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.900%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3779468</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>946</v>
+        <v>43927</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>493777</t>
+          <t>77131999</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>24.400%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-17.500%</t>
+          <t>1.900%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2094,7 +2189,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>GECC-134628136</t>
+          <t>ALSE-134328097</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2104,12 +2199,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134328097/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2121,55 +2221,55 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>27.100%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>20.900%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>46373640</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>468</v>
+        <v>118778</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>313322</t>
+          <t>221883447</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>22.000%</t>
+          <t>21.700%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-15.200%</t>
+          <t>17.900%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2179,7 +2279,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>GECC-134629877</t>
+          <t>ALSE-134345731</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2189,12 +2289,17 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629877/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134345731/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2206,12 +2311,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>03/18/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2221,7 +2326,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2231,30 +2336,30 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-13.700%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-109613</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>6838</v>
+        <v>472</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3570611</t>
+          <t>800092</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>22.700%</t>
+          <t>13.700%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-18.900%</t>
+          <t>-32.200%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2264,7 +2369,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>GECC-134629950</t>
+          <t>ALSE-134416811</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2274,12 +2379,17 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134416811/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2291,12 +2401,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2306,7 +2416,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2325,21 +2435,21 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1090</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>851643</t>
+          <t>541730713</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>22.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-19.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2349,7 +2459,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>GECC-134629950</t>
+          <t>ALSE-134489276</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2359,12 +2469,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134489276/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2376,12 +2491,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2391,7 +2506,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2410,21 +2525,21 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>220</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>268980</t>
+          <t>6895556</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>19.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-15.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2434,7 +2549,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>GECC-134629950</t>
+          <t>ALSE-134489925</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2444,12 +2559,17 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134489925/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2461,12 +2581,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>07/24/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2486,30 +2606,30 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.900%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-20025</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>136399</v>
+        <v>472</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>202923596</t>
+          <t>690507</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-8.200%</t>
+          <t>-5.700%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2519,7 +2639,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>PRGS-134191751</t>
+          <t>ALSE-134500694</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2529,12 +2649,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134500694/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2546,55 +2671,55 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>01/19/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.900%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.900%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>675285</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>314349</v>
+        <v>6107</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>306405692</t>
+          <t>5681808</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>11.300%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>5.600%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2604,7 +2729,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>PRGS-134191751</t>
+          <t>ALSE-134517504</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2614,12 +2739,17 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134517504/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2631,12 +2761,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>03/16/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2646,35 +2776,35 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10.200%</t>
+          <t>6.900%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>6.900%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>986227</t>
+          <t>1129791</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>21127</v>
+        <v>3980</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>9923754</t>
+          <t>16373783</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>12.600%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2689,7 +2819,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>LBPM-134220016</t>
+          <t>ALSE-134538132</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2699,12 +2829,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134220016/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134538132/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2716,12 +2851,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>12/31/2025</t>
+          <t>08/04/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2731,40 +2866,40 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>18.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>4.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>563934</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>11751</v>
+        <v>123621</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11487151</t>
+          <t>233084721</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>6.800%</t>
+          <t>4.200%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>-3.700%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2774,7 +2909,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>LBPM-134619371</t>
+          <t>ALSE-134572006</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2784,12 +2919,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134572006/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2801,45 +2941,45 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-3.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>-2.400%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-273240</t>
+          <t>-313375</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>36921</v>
+        <v>8451</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8303864</t>
+          <t>13057296</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2849,7 +2989,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-37.500%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2859,7 +2999,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>LBPM-134745236</t>
+          <t>ALSE-134597553</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2869,12 +3009,17 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134597553/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2886,50 +3031,55 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>21.500%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>10650679</t>
+          <t>-1425594</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>59070</v>
+        <v>27336</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>49543045</t>
+          <t>43199831</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>22.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-9.200%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2939,7 +3089,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>SFMA-134315085</t>
+          <t>ALSE-134684477</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2949,12 +3099,17 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134315085/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134684477/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -2966,50 +3121,55 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>04/15/2026</t>
+          <t>07/12/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>22.500%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>93.700%</t>
+          <t>19.600%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2706726</t>
+          <t>4031402</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>8405</v>
+        <v>6098</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2888541</t>
+          <t>20568379</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>108.400%</t>
+          <t>32.700%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>31.400%</t>
+          <t>8.500%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3019,7 +3179,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>SFMA-134315091</t>
+          <t>ALSE-134095154</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3029,12 +3189,17 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134315091/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134095154/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
         </is>
       </c>
     </row>
@@ -3046,12 +3211,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>08/01/2025</t>
+          <t>07/12/2025</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3061,35 +3226,40 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>27.900%</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>23.900%</t>
+          <t>27.900%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3367834</t>
+          <t>3634220</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>17873</v>
+        <v>6809</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>14091908</t>
+          <t>13025878</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>27.700%</t>
+          <t>28.800%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>5.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3099,7 +3269,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>SFMA-134422784</t>
+          <t>ALSE-134095177</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3109,12 +3279,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134422784/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134095177/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
         </is>
       </c>
     </row>
@@ -3126,50 +3301,50 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>02/08/2025</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>31.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>21.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>10657508</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>39456</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>50509518</t>
+          <t>18275978</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>33.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3184,7 +3359,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>TRVD-G134262689</t>
+          <t>ALSE-134214686</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3194,12 +3369,17 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134214686/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -3209,52 +3389,47 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>02/08/2025</t>
-        </is>
-      </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>31.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>21.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>636936</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2461</v>
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2976338</t>
+          <t>22469034</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>32.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3269,7 +3444,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>TRVD-G134262689</t>
+          <t>GMMX-134645542</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3279,12 +3454,17 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134645542/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>
@@ -3296,80 +3476,4515 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>12/13/2025</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>5324</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>22469034</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>GMMX-134659152</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134659152/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>07/18/2024</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>GEICO Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>18641</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>10082975</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>65.900%</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-53.960%</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>GECC-134044540</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134044540/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>10/10/2024</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GEICO General Insurance Company</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>42889</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>83538733</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>126.400%</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-39.700%</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>GECC-134126215</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134126215/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>10/10/2024</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Government Employees Insurance Company</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>12607</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>25367953</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>126.500%</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-20.400%</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>GECC-134126215</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134126215/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>10/10/2024</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GEICO Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>10898</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>29466421</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>41.300%</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>-23.900%</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>GECC-134126294</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134126294/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>10/10/2024</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>GEICO Advantage Insurance Company</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>182963</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>340981796</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>126.600%</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-43.700%</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>GECC-134126318</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>10/10/2024</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GEICO Choice Insurance Company</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>70409</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>162085401</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>122.200%</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-40.600%</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>GECC-134126318</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>10/10/2024</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>GEICO Secure Insurance Company</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>24488</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>73529867</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>146.400%</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-45.400%</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>GECC-134126318</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>09/18/2025</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GEICO General Insurance Company</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>2090</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1077172</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>24.800%</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-17.900%</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>GECC-134628136</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>09/18/2025</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Government Employees Insurance Company</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>946</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>493777</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>24.400%</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-17.500%</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>GECC-134628136</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>09/18/2025</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>GEICO Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>468</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>313322</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>22.000%</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>-15.200%</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>GECC-134629877</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134629877/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>09/18/2025</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>GEICO Advantage Insurance Company</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>6838</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3570611</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>22.700%</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-18.900%</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>GECC-134629950</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>09/18/2025</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GEICO Choice Insurance Company</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>1090</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>851643</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>22.200%</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>-19.000%</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>GECC-134629950</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>09/18/2025</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GEICO Secure Insurance Company</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>220</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>268980</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>19.400%</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>-15.800%</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>GECC-134629950</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>03/01/2024</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>27.500%</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>23.900%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3820239</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>9954</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>15970300</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>46.200%</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>2.200%</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>LBPM-133883711</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>2023-11-10</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133883711/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>05/26/2024</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>16.300%</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>6.400%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1119411</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>10384</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>17592601</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>29.769%</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2.200%</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>LBPM-133977065</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>2024-02-01</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133977065/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>04/26/2024</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>12.800%</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>12.000%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>22813593</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>133404</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>190113279</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>21.000%</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>3.500%</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>PRGS-133899969</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133899969/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>04/26/2024</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>12.500%</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>10.600%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>29992321</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>300545</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>282946429</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>21.700%</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>3.300%</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>PRGS-133899969</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2023-11-28</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133899969/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Progressive Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>136399</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>202923596</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>8.800%</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>-8.200%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>PRGS-134191751</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>02/07/2025</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Progressive Direct Insurance Company</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>314349</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>306405692</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>11.300%</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>-8.500%</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>PRGS-134191751</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>03/12/2024</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>General Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>8.700%</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>7.000%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>8</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>11561</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>14.000%</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>4.000%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>LBPM-133779020</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>03/12/2024</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>8.700%</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>8.300%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>76044</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>505</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>913384</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>34.000%</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2.000%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>LBPM-133779020</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>03/12/2024</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>8.700%</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>8.000%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>7848312</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>45298</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>98199451</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>34.000%</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>LBPM-133779020</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>06/19/2024</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>12.600%</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>12.600%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1219491</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>22355</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>9701188</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>25.700%</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>LBPM-133864197</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133864197/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>01/09/2024</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>25.800%</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>15.200%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>54501941</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>215944</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>357929733</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>58.700%</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>LBPM-133864423</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2023-10-26</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133864423/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>04/27/2024</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>17.000%</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>14.600%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>63341742</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>260540</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>434561908</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>39.600%</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>-9.100%</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>LBPM-133979163</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2024-02-05</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133979163/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>09/22/2024</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>General Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>16.200%</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>18.400%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2260</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>7</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>12289</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>24.400%</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>15.500%</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>LBPM-134049356</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>09/22/2024</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>16.200%</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>17.100%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>160434</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>486</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>939400</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>31.700%</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>9.900%</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>LBPM-134049356</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>09/22/2024</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>16.200%</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>16.000%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>16499437</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>43948</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>103370288</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>33.100%</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>LBPM-134049356</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2024-03-29</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>09/22/2024</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Oregon</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>22.300%</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>22.100%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2162665</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>4597</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>9794277</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>37.000%</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>LBPM-134066961</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2024-04-16</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134066961/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>03/16/2025</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of Illinois</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>10.200%</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>9.900%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>986227</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>21127</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>9923754</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>13.700%</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>LBPM-134220016</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134220016/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>12/31/2025</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>04.0001 Condominium Homeowners</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>18.800%</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>4.900%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>563934</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>11751</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>11487151</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>6.800%</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0.500%</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>LBPM-134619371</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>02/21/2026</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-3.100%</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-3.300%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-273240</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>36921</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>8303864</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>-37.500%</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>LBPM-134745236</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>02/01/2024</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>04.0002 Mobile Homeowners</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0.500%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>62226</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>17675</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>13517575</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>SFMA-133686505</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2023-07-05</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133686505/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>01/08/2024</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>34.400%</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>17.100%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>23629247</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>75857</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>137915446</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>63.200%</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>-3.800%</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>SFMA-133737144</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133737144/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>01/08/2024</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>18.000%</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>15.600%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>171989837</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>1193339</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1103919578</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>40.000%</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-5.400%</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>SFMA-133737144</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2023-07-21</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133737144/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>06/10/2024</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>32.800%</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>14.500%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>25053420</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>81718</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>172527324</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>SFMA-133957681</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2024-02-02</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133957681/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>06/10/2024</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>16.600%</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>13.800%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>175723240</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>1197563</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>1275343795</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>SFMA-133957681</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2024-02-02</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133957681/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>07/15/2024</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>17.900%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>69353041</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>525150</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>387128333</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>31.200%</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>SFMA-134044384</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134044384/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>08/01/2024</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>2020</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>1139756</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>10.000%</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-9.500%</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>SFMA-134076828</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134076828/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>08/01/2024</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>33343</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>9698904</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>9.500%</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-9.000%</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>SFMA-134076828</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134076828/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>12/15/2025</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>21.500%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>10650679</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>59070</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>49543045</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>22.800%</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>SFMA-134315085</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134315085/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>93.700%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2706726</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>8405</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2888541</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>108.400%</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>31.400%</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>SFMA-134315091</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134315091/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>08/01/2025</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>04.0002 Mobile Homeowners</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>23.900%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>3367834</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>17873</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>14091908</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>27.700%</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>5.100%</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>SFMA-134422784</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134422784/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>02/25/2024</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>3955</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>7784317</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>TRVD-133853983</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133853983/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>02/25/2024</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>783</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>1381984</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>TRVD-133853983</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133853983/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>05/03/2025</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>41.800%</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>33.500%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>163</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>59.400%</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>13.300%</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>TRVD-134151094</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134151094/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>ambest_window_unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>12/13/2024</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>36.100%</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>21.600%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>20285484</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>74773</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>93914279</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>64.300%</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>TRVD-G134214259</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134220061/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>02/08/2025</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>31.500%</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>21.100%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>10657508</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>39456</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>50509518</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>33.400%</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>TRVD-G134262689</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>02/08/2025</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>31.500%</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>21.400%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>636936</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>2461</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2976338</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>32.600%</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>TRVD-G134262689</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>03/30/2025</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>The Travelers Home and Marine Insurance Company</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>19.0 Personal Auto</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I35" t="n">
+      <c r="I85" t="n">
         <v>2483</v>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>4953073</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>TRVD-G134336116</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
         <is>
           <t>2024-12-19</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>output/pdfs/WA/134358134/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>ambest_validated</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R85"/>
+  <dimension ref="A1:T85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>validation_tier</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>external_validation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -597,6 +607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,6 +707,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -777,6 +807,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -867,6 +907,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -957,6 +1007,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1042,6 +1102,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1132,6 +1202,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1222,6 +1302,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1312,6 +1402,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1402,6 +1502,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1492,6 +1602,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1582,6 +1702,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1669,7 +1799,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -1762,6 +1902,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1852,6 +2002,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1942,6 +2102,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2029,7 +2199,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2299,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2399,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2499,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2599,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2699,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2799,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2659,7 +2899,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2999,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2839,7 +3099,17 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2929,7 +3199,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3299,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3399,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3202,6 +3502,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3292,6 +3602,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3379,7 +3699,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3794,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3894,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3647,6 +3997,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3737,6 +4097,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3827,6 +4197,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3917,6 +4297,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4007,6 +4397,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4097,6 +4497,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4187,6 +4597,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4274,7 +4694,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4364,7 +4794,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4894,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4994,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4634,7 +5094,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4724,7 +5194,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4817,6 +5297,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4907,6 +5397,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4997,6 +5497,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5087,6 +5597,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5174,7 +5694,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5794,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5357,6 +5897,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5447,6 +5997,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5537,6 +6097,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5627,6 +6197,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5717,6 +6297,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5807,6 +6397,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5897,6 +6497,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5987,6 +6597,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6077,6 +6697,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6167,6 +6797,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6254,7 +6894,17 @@
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6344,7 +6994,17 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6434,7 +7094,17 @@
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -6512,6 +7182,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6602,6 +7282,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6692,6 +7382,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6772,6 +7472,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6852,6 +7562,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6937,6 +7657,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7027,6 +7757,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7117,6 +7857,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7199,7 +7949,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7284,7 +8044,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7369,7 +8139,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7457,6 +8237,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -7542,6 +8332,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -7627,6 +8427,16 @@
           <t>ambest_window_unmatched</t>
         </is>
       </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>unvalidatable</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -7717,6 +8527,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -7804,7 +8624,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7894,7 +8724,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7984,7 +8824,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T85"/>
+  <dimension ref="A1:U85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
           <t>external_validation</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>match_strength</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -614,9 +619,10 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -714,9 +720,10 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -814,9 +821,10 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -914,9 +922,10 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1014,9 +1023,10 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1109,9 +1119,10 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1209,9 +1220,10 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1309,9 +1321,10 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1399,7 +1412,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1409,9 +1422,10 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1499,7 +1513,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1509,9 +1523,10 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1609,9 +1624,10 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1709,9 +1725,10 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1809,9 +1826,10 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1909,9 +1927,10 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2009,9 +2028,10 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2109,9 +2129,10 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2209,9 +2230,10 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2309,9 +2331,10 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2409,9 +2432,10 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2509,9 +2533,10 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2609,9 +2634,10 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2709,9 +2735,10 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2809,9 +2836,10 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2909,9 +2937,10 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3009,9 +3038,10 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3109,9 +3139,10 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3209,9 +3240,10 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3309,9 +3341,10 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3409,9 +3442,10 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3499,7 +3533,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3509,9 +3543,10 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3599,7 +3634,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3609,9 +3644,10 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3709,9 +3745,10 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3804,9 +3841,10 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3904,9 +3942,10 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4004,9 +4043,10 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4104,9 +4144,10 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4204,9 +4245,10 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4304,9 +4346,10 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4404,9 +4447,10 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4504,9 +4548,10 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4604,9 +4649,10 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4704,9 +4750,10 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4804,9 +4851,10 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4904,9 +4952,10 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5004,9 +5053,10 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5104,9 +5154,10 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5204,9 +5255,10 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5304,9 +5356,10 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5404,9 +5457,10 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5504,9 +5558,10 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5604,9 +5659,10 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5704,9 +5760,10 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5804,9 +5861,10 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5904,9 +5962,10 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6004,9 +6063,10 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6104,9 +6164,10 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6204,9 +6265,10 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6304,9 +6366,10 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6404,9 +6467,10 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6504,9 +6568,10 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6604,9 +6669,10 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6704,9 +6770,10 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6804,9 +6871,10 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6904,9 +6972,10 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7004,9 +7073,10 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7104,9 +7174,10 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7189,9 +7260,10 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7289,9 +7361,10 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7389,9 +7462,10 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7479,9 +7553,10 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7569,9 +7644,10 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7664,9 +7740,10 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7764,9 +7841,10 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7864,9 +7942,10 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7959,9 +8038,10 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8054,9 +8134,10 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8149,9 +8230,10 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8244,9 +8326,10 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8339,9 +8422,10 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8424,7 +8508,7 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>ambest_window_unmatched</t>
+          <t>pipeline_only</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -8434,9 +8518,10 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>unvalidatable</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8534,9 +8619,10 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8634,9 +8720,10 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8734,9 +8821,10 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8834,9 +8922,10 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U85"/>
+  <dimension ref="A1:U86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,7 +622,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -723,7 +722,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -824,7 +822,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -925,7 +922,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1026,7 +1022,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1122,7 +1117,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1223,7 +1217,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1324,7 +1317,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1425,7 +1417,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1526,7 +1517,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1627,7 +1617,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1728,7 +1717,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1829,7 +1817,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1930,7 +1917,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2031,7 +2017,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2132,7 +2117,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2233,7 +2217,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2334,7 +2317,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2435,7 +2417,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2536,7 +2517,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2637,7 +2617,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2738,7 +2717,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2839,7 +2817,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2940,7 +2917,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3041,7 +3017,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3142,7 +3117,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3243,7 +3217,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3344,7 +3317,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3445,7 +3417,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3546,7 +3517,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3647,7 +3617,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3748,7 +3717,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3844,7 +3812,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3945,7 +3912,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4046,7 +4012,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4147,7 +4112,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4248,7 +4212,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4349,7 +4312,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4450,7 +4412,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4551,7 +4512,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4652,7 +4612,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4753,7 +4712,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4854,7 +4812,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4955,7 +4912,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5056,7 +5012,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5157,7 +5112,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5258,7 +5212,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5359,7 +5312,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5460,7 +5412,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5561,7 +5512,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5662,7 +5612,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5763,7 +5712,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5864,7 +5812,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5965,7 +5912,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6066,7 +6012,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6167,7 +6112,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6268,7 +6212,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6369,7 +6312,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6470,7 +6412,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6571,7 +6512,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6672,7 +6612,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6773,7 +6712,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6874,7 +6812,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6975,7 +6912,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7076,7 +7012,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7177,7 +7112,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7263,7 +7197,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7364,7 +7297,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7465,7 +7397,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7556,7 +7487,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7647,7 +7577,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7743,7 +7672,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7844,7 +7772,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7945,7 +7872,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8041,7 +7967,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8137,7 +8062,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8233,7 +8157,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8329,7 +8252,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8425,7 +8347,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8521,7 +8442,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8622,7 +8542,6 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8723,7 +8642,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8824,7 +8742,6 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8925,7 +8842,101 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>03/30/2025</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>495</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>910721</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>TRVD-G134336116</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134358134/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U86"/>
+  <dimension ref="A1:U98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01/15/2024</t>
+          <t>12/18/2023</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -551,35 +551,35 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.700%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>20.400%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>99983292</t>
+          <t>1260235</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>194444</v>
+        <v>10798</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>490114177</t>
+          <t>26254894</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>31.300%</t>
+          <t>14.700%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>ALSE-133789684</t>
+          <t>ALSE-133733118</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -599,12 +599,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2023-08-22</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133789684/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133733118/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -622,6 +622,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -631,55 +632,55 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>02/26/2024</t>
+          <t>01/15/2024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8.700%</t>
+          <t>20.700%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>3.200%</t>
+          <t>20.400%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>814476</t>
+          <t>99983292</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>14343</v>
+        <v>194444</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>25452380</t>
+          <t>490114177</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.400%</t>
+          <t>31.300%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.700%</t>
+          <t>5.700%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -689,7 +690,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>ALSE-133897373</t>
+          <t>ALSE-133789684</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -699,12 +700,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2023-11-20</t>
+          <t>2023-08-22</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133897373/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133789684/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -722,6 +723,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -736,7 +738,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -751,35 +753,35 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>8.700%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.600%</t>
+          <t>3.200%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5108310</t>
+          <t>814476</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>48054</v>
+        <v>14343</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>77398640</t>
+          <t>25452380</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>5.400%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2.400%</t>
+          <t>1.700%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -789,7 +791,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>ALSE-133897486</t>
+          <t>ALSE-133897373</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -804,7 +806,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133897486/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133897373/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -822,6 +824,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -836,7 +839,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -851,35 +854,35 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>10.200%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>6.600%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1408003</t>
+          <t>5108310</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>18389</v>
+        <v>48054</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>29333392</t>
+          <t>77398640</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.600%</t>
+          <t>2.400%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -889,7 +892,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ALSE-133902389</t>
+          <t>ALSE-133897486</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -899,12 +902,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133902389/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133897486/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -922,6 +925,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -931,12 +935,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>03/11/2024</t>
+          <t>02/26/2024</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -951,35 +955,35 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.500%</t>
+          <t>10.200%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>39.900%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>56647288</t>
+          <t>1408003</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>106686</v>
+        <v>18389</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>141973154</t>
+          <t>29333392</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>109.800%</t>
+          <t>8.800%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>16.700%</t>
+          <t>2.600%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -989,7 +993,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ALSE-133920075</t>
+          <t>ALSE-133902389</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -999,12 +1003,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2023-12-12</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133920075/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133902389/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1022,6 +1026,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1031,50 +1036,55 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>04/15/2024</t>
+          <t>03/11/2024</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>65.500%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>39.900%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56647288</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>194444</v>
+        <v>106686</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>602924930</t>
+          <t>141973154</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>84.600%</t>
+          <t>109.800%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-3.400%</t>
+          <t>16.700%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1084,7 +1094,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ALSE-133975008</t>
+          <t>ALSE-133920075</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1094,12 +1104,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2023-12-12</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133975008/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133920075/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1117,6 +1127,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1126,7 +1137,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>08/12/2024</t>
+          <t>04/15/2024</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1144,11 +1155,6 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>0.000%</t>
@@ -1160,21 +1166,21 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>194444</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>413455792</t>
+          <t>602924930</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>84.600%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.400%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1184,7 +1190,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>ALSE-134098985</t>
+          <t>ALSE-133975008</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1194,12 +1200,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2024-05-08</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134098985/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133975008/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1217,6 +1223,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1231,7 +1238,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1241,7 +1248,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1264,7 +1271,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6928058</t>
+          <t>413455792</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1284,7 +1291,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>ALSE-134099016</t>
+          <t>ALSE-134098985</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1299,7 +1306,7 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134099016/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134098985/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1317,6 +1324,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1326,55 +1334,55 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>03/24/2025</t>
+          <t>08/12/2024</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>926592</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>9705</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11699459</t>
+          <t>6928058</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>10.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1384,7 +1392,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>ALSE-134119095</t>
+          <t>ALSE-134099016</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1394,12 +1402,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-08</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134119095/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134099016/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1414,9 +1422,10 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1426,7 +1435,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>02/17/2025</t>
+          <t>03/24/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1436,45 +1445,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>16.500%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>13.400%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2392710</t>
+          <t>926592</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5557</v>
+        <v>9705</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17856043</t>
+          <t>11699459</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>24.800%</t>
+          <t>10.400%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.500%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1484,7 +1493,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>ALSE-134135043</t>
+          <t>ALSE-134119095</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1494,12 +1503,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2024-06-05</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134135043/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134119095/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1517,6 +1526,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1526,12 +1536,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>09/23/2024</t>
+          <t>02/17/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1546,30 +1556,30 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>16.400%</t>
+          <t>16.500%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>13.400%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1880630</t>
+          <t>2392710</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>26873</v>
+        <v>5557</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>62687682</t>
+          <t>17856043</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>8.200%</t>
+          <t>24.800%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1584,7 +1594,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>ALSE-134138722</t>
+          <t>ALSE-134135043</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1594,12 +1604,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2024-06-07</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134138722/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134135043/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1614,9 +1624,10 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1631,7 +1642,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1646,35 +1657,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>20.900%</t>
+          <t>16.400%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>10.800%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2874136</t>
+          <t>1880630</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>10248</v>
+        <v>26873</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>26612374</t>
+          <t>62687682</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>17.800%</t>
+          <t>8.200%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1684,7 +1695,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>ALSE-134142123</t>
+          <t>ALSE-134138722</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1694,12 +1705,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-07</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134142123/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134138722/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1717,6 +1728,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1726,12 +1738,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>02/03/2025</t>
+          <t>09/23/2024</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1746,35 +1758,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>9.600%</t>
+          <t>20.900%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>9.100%</t>
+          <t>10.800%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>55166401</t>
+          <t>2874136</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>200145</v>
+        <v>10248</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>606224182</t>
+          <t>26612374</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>48.000%</t>
+          <t>17.800%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-1.000%</t>
+          <t>0.800%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1784,7 +1796,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>ALSE-134206307</t>
+          <t>ALSE-134142123</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1794,12 +1806,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134206307/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134142123/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1809,14 +1821,15 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1826,12 +1839,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11/25/2024</t>
+          <t>02/03/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1846,35 +1859,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.600%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>55166401</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>200145</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>61240239</t>
+          <t>606224182</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>48.000%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.000%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1884,7 +1897,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>ALSE-134214513</t>
+          <t>ALSE-134206307</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1894,12 +1907,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134214513/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134206307/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1909,14 +1922,15 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1931,7 +1945,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1964,7 +1978,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24887220</t>
+          <t>61240239</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2017,6 +2031,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2031,7 +2046,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2064,7 +2079,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>15804620</t>
+          <t>24887220</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2117,6 +2132,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2126,7 +2142,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>08/25/2025</t>
+          <t>11/25/2024</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2136,45 +2152,45 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>17.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>11.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2752700</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>13118</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>23936525</t>
+          <t>15804620</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>13.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>7.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2184,7 +2200,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>ALSE-134326701</t>
+          <t>ALSE-134214513</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -2194,12 +2210,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2024-11-20</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134326701/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134214513/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2209,14 +2225,15 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2231,7 +2248,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2246,35 +2263,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>15.000%</t>
+          <t>17.900%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8.900%</t>
+          <t>11.500%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2542799</t>
+          <t>2752700</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>17045</v>
+        <v>13118</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>28570771</t>
+          <t>23936525</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>10.500%</t>
+          <t>13.200%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5.500%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2284,7 +2301,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>ALSE-134327525</t>
+          <t>ALSE-134326701</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2294,12 +2311,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-11-20</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134327525/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134326701/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2317,6 +2334,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2331,7 +2349,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2346,35 +2364,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>11.400%</t>
+          <t>15.000%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4.900%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3779468</t>
+          <t>2542799</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>43927</v>
+        <v>17045</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77131999</t>
+          <t>28570771</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8.900%</t>
+          <t>10.500%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.900%</t>
+          <t>5.500%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2384,7 +2402,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>ALSE-134328097</t>
+          <t>ALSE-134327525</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2399,7 +2417,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134328097/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134327525/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -2417,6 +2435,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2426,12 +2445,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04/07/2025</t>
+          <t>08/25/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2446,35 +2465,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>27.100%</t>
+          <t>11.400%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20.900%</t>
+          <t>4.900%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>46373640</t>
+          <t>3779468</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>118778</v>
+        <v>43927</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>221883447</t>
+          <t>77131999</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>21.700%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>17.900%</t>
+          <t>1.900%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2484,7 +2503,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>ALSE-134345731</t>
+          <t>ALSE-134328097</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2494,12 +2513,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2024-12-09</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134345731/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134328097/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2517,6 +2536,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2526,55 +2546,55 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>03/18/2025</t>
+          <t>04/07/2025</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>27.100%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-13.700%</t>
+          <t>20.900%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-109613</t>
+          <t>46373640</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>472</v>
+        <v>118778</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>800092</t>
+          <t>221883447</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>21.700%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-32.200%</t>
+          <t>17.900%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2584,7 +2604,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>ALSE-134416811</t>
+          <t>ALSE-134345731</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2594,12 +2614,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2024-12-09</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134416811/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134345731/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2617,6 +2637,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2626,12 +2647,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>07/21/2025</t>
+          <t>03/18/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2651,30 +2672,30 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-13.700%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-109613</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>472</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>541730713</t>
+          <t>800092</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.700%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-32.200%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2684,7 +2705,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>ALSE-134489276</t>
+          <t>ALSE-134416811</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2694,12 +2715,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134489276/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134416811/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2717,6 +2738,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2731,7 +2753,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2741,7 +2763,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2764,7 +2786,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6895556</t>
+          <t>541730713</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -2784,7 +2806,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>ALSE-134489925</t>
+          <t>ALSE-134489276</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2799,7 +2821,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134489925/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134489276/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2817,6 +2839,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2826,12 +2849,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>07/24/2025</t>
+          <t>07/21/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2841,7 +2864,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2851,30 +2874,30 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-20025</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>472</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>690507</t>
+          <t>6895556</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-5.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2884,7 +2907,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>ALSE-134500694</t>
+          <t>ALSE-134489925</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2894,12 +2917,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2025-04-17</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134500694/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134489925/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2917,6 +2940,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2926,55 +2950,55 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01/19/2026</t>
+          <t>07/24/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>11.900%</t>
+          <t>-2.900%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>675285</t>
+          <t>-20025</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>6107</v>
+        <v>472</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>5681808</t>
+          <t>690507</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>5.600%</t>
+          <t>-5.700%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2984,7 +3008,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>ALSE-134517504</t>
+          <t>ALSE-134500694</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2994,12 +3018,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134517504/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134500694/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3017,6 +3041,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3026,55 +3051,55 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>01/19/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>6.900%</t>
+          <t>11.900%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>6.900%</t>
+          <t>11.900%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1129791</t>
+          <t>675285</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3980</v>
+        <v>6107</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>16373783</t>
+          <t>5681808</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>12.600%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.600%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3084,7 +3109,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>ALSE-134538132</t>
+          <t>ALSE-134517504</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -3094,12 +3119,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-05-01</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134538132/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134517504/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3117,6 +3142,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3126,55 +3152,55 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>08/04/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.900%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.900%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1129791</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>123621</v>
+        <v>3980</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>233084721</t>
+          <t>16373783</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>4.200%</t>
+          <t>12.600%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-3.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3184,7 +3210,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>ALSE-134572006</t>
+          <t>ALSE-134538132</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -3194,12 +3220,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134572006/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134538132/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3217,6 +3243,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3226,22 +3253,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>10/14/2025</t>
+          <t>08/04/2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3251,30 +3278,30 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-313375</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8451</v>
+        <v>123621</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>13057296</t>
+          <t>233084721</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.200%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-5.000%</t>
+          <t>-3.700%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -3284,7 +3311,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>ALSE-134597553</t>
+          <t>ALSE-134572006</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3294,12 +3321,12 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134597553/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134572006/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3317,6 +3344,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3326,7 +3354,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11/18/2025</t>
+          <t>10/14/2025</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3351,20 +3379,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>-2.400%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-1425594</t>
+          <t>-313375</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>27336</v>
+        <v>8451</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>43199831</t>
+          <t>13057296</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -3374,7 +3402,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-9.200%</t>
+          <t>-5.000%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3384,7 +3412,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>ALSE-134684477</t>
+          <t>ALSE-134597553</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -3394,12 +3422,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134684477/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134597553/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3417,6 +3445,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3426,12 +3455,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>07/12/2025</t>
+          <t>11/18/2025</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3446,35 +3475,35 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>22.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19.600%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4031402</t>
+          <t>-1425594</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>6098</v>
+        <v>27336</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>20568379</t>
+          <t>43199831</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>32.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>8.500%</t>
+          <t>-9.200%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3484,7 +3513,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>ALSE-134095154</t>
+          <t>ALSE-134684477</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -3494,12 +3523,12 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134095154/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134684477/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3509,7 +3538,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3517,6 +3546,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3526,55 +3556,50 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>07/12/2025</t>
+          <t>04/21/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>27.900%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>27.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>3634220</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>6809</v>
+        <v>41589</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>13025878</t>
+          <t>127130842</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>28.800%</t>
+          <t>1.700%</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-37.500%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3584,7 +3609,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>ALSE-134095177</t>
+          <t>ALSE-134858576</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -3594,12 +3619,12 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2024-05-07</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134095177/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134858576/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3609,7 +3634,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3617,6 +3642,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3626,7 +3652,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01/06/2025</t>
+          <t>07/12/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3646,35 +3672,35 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>22.500%</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>19.600%</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4031402</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>6098</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>18275978</t>
+          <t>20568379</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>32.700%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.500%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3684,7 +3710,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>ALSE-134214686</t>
+          <t>ALSE-134095154</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3694,12 +3720,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134214686/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134095154/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3709,7 +3735,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3717,6 +3743,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3724,6 +3751,11 @@
           <t>WA</t>
         </is>
       </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>07/12/2025</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
           <t>Encompass Indemnity Company</t>
@@ -3731,40 +3763,40 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>27.900%</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>27.900%</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3634220</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>6809</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>22469034</t>
+          <t>13025878</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>28.800%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3779,7 +3811,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>GMMX-134645542</t>
+          <t>ALSE-134095177</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3789,12 +3821,12 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-05-07</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134645542/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134095177/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3804,14 +3836,15 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3821,7 +3854,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12/13/2025</t>
+          <t>01/06/2025</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3855,11 +3888,11 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>5324</v>
+        <v>0</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>22469034</t>
+          <t>18275978</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -3879,7 +3912,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>GMMX-134659152</t>
+          <t>ALSE-134214686</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3889,12 +3922,12 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134659152/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134214686/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3912,6 +3945,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3919,14 +3953,9 @@
           <t>WA</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>07/18/2024</t>
-        </is>
-      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3936,7 +3965,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3955,21 +3984,21 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>18641</v>
+        <v>0</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>10082975</t>
+          <t>22469034</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>65.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-53.960%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3979,7 +4008,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>GECC-134044540</t>
+          <t>GMMX-134645542</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3989,12 +4018,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134044540/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134645542/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -4004,14 +4033,15 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4021,12 +4051,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>12/13/2025</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4055,21 +4085,21 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>42889</v>
+        <v>5324</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>83538733</t>
+          <t>22469034</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>126.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-39.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4079,7 +4109,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>GECC-134126215</t>
+          <t>GMMX-134659152</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4089,12 +4119,12 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134126215/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134659152/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4104,14 +4134,15 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4121,12 +4152,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>07/18/2024</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4136,7 +4167,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4155,21 +4186,21 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>12607</v>
+        <v>18641</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>25367953</t>
+          <t>10082975</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>126.500%</t>
+          <t>65.900%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-20.400%</t>
+          <t>-53.960%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4179,7 +4210,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>GECC-134126215</t>
+          <t>GECC-134044540</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4189,12 +4220,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134126215/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134044540/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4212,6 +4243,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4226,7 +4258,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4255,21 +4287,21 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>10898</v>
+        <v>42889</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>29466421</t>
+          <t>83538733</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>41.300%</t>
+          <t>126.400%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-23.900%</t>
+          <t>-39.700%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4279,7 +4311,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>GECC-134126294</t>
+          <t>GECC-134126215</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4294,7 +4326,7 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134126294/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134126215/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -4312,6 +4344,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4326,7 +4359,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4355,21 +4388,21 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>182963</v>
+        <v>12607</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>340981796</t>
+          <t>25367953</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>126.600%</t>
+          <t>126.500%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-43.700%</t>
+          <t>-20.400%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4379,7 +4412,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>GECC-134126318</t>
+          <t>GECC-134126215</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4394,7 +4427,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134126215/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4412,6 +4445,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4426,7 +4460,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4455,21 +4489,21 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>70409</v>
+        <v>10898</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>162085401</t>
+          <t>29466421</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>122.200%</t>
+          <t>41.300%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-40.600%</t>
+          <t>-23.900%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4479,7 +4513,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>GECC-134126318</t>
+          <t>GECC-134126294</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4494,7 +4528,7 @@
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134126294/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4512,6 +4546,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4526,7 +4561,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4555,21 +4590,21 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>24488</v>
+        <v>182963</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>73529867</t>
+          <t>340981796</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>146.400%</t>
+          <t>126.600%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-45.400%</t>
+          <t>-43.700%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4612,6 +4647,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4621,12 +4657,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4636,7 +4672,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4655,21 +4691,21 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2090</v>
+        <v>70409</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1077172</t>
+          <t>162085401</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>24.800%</t>
+          <t>122.200%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-17.900%</t>
+          <t>-40.600%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4679,7 +4715,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>GECC-134628136</t>
+          <t>GECC-134126318</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4689,12 +4725,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4704,14 +4740,15 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4721,12 +4758,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4736,7 +4773,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4755,21 +4792,21 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>946</v>
+        <v>24488</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>493777</t>
+          <t>73529867</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>24.400%</t>
+          <t>146.400%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-17.500%</t>
+          <t>-45.400%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4779,7 +4816,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>GECC-134628136</t>
+          <t>GECC-134126318</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4789,12 +4826,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4804,14 +4841,15 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4826,7 +4864,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4855,21 +4893,21 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>468</v>
+        <v>2090</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>313322</t>
+          <t>1077172</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>22.000%</t>
+          <t>24.800%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-15.200%</t>
+          <t>-17.900%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4879,7 +4917,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>GECC-134629877</t>
+          <t>GECC-134628136</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4894,7 +4932,7 @@
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629877/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4912,6 +4950,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4926,7 +4965,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4955,21 +4994,21 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6838</v>
+        <v>946</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>3570611</t>
+          <t>493777</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>22.700%</t>
+          <t>24.400%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-18.900%</t>
+          <t>-17.500%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4979,7 +5018,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>GECC-134629950</t>
+          <t>GECC-134628136</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4994,7 +5033,7 @@
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -5012,6 +5051,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5026,7 +5066,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5055,21 +5095,21 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1090</v>
+        <v>468</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>851643</t>
+          <t>313322</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>22.200%</t>
+          <t>22.000%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-19.000%</t>
+          <t>-15.200%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5079,7 +5119,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>GECC-134629950</t>
+          <t>GECC-134629877</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5094,7 +5134,7 @@
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134629877/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -5112,6 +5152,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5126,7 +5167,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5155,21 +5196,21 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>220</v>
+        <v>6838</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>268980</t>
+          <t>3570611</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>19.400%</t>
+          <t>22.700%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-15.800%</t>
+          <t>-18.900%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5212,6 +5253,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5221,55 +5263,55 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>03/01/2024</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>27.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>23.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3820239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>9954</v>
+        <v>1090</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>15970300</t>
+          <t>851643</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>46.200%</t>
+          <t>22.200%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2.200%</t>
+          <t>-19.000%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5279,7 +5321,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>LBPM-133883711</t>
+          <t>GECC-134629950</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5289,12 +5331,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133883711/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5304,14 +5346,15 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5321,55 +5364,55 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>05/26/2024</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>16.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>6.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1119411</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>10384</v>
+        <v>220</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>17592601</t>
+          <t>268980</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>29.769%</t>
+          <t>19.400%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2.200%</t>
+          <t>-15.800%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5379,7 +5422,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>LBPM-133977065</t>
+          <t>GECC-134629950</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5389,12 +5432,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133977065/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5404,14 +5447,15 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5421,12 +5465,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>04/26/2024</t>
+          <t>04/30/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5441,35 +5485,35 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>12.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>12.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>22813593</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>133404</v>
+        <v>0</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>190113279</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>21.000%</t>
+          <t>59.800%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>-24.600%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5479,7 +5523,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>PRGS-133899969</t>
+          <t>GECC-134879681</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5489,12 +5533,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133899969/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134879681/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5504,14 +5548,15 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5521,12 +5566,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>04/26/2024</t>
+          <t>04/30/2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5541,35 +5586,35 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>29992321</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>300545</v>
+        <v>0</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>282946429</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>21.700%</t>
+          <t>44.800%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>3.300%</t>
+          <t>-25.000%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5579,7 +5624,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>PRGS-133899969</t>
+          <t>GECC-134879681</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5589,12 +5634,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133899969/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134879681/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5604,14 +5649,15 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5621,12 +5667,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/30/2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5655,21 +5701,21 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>136399</v>
+        <v>0</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>202923596</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>35.300%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-8.200%</t>
+          <t>-15.500%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5679,7 +5725,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>PRGS-134191751</t>
+          <t>GECC-134881446</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5689,12 +5735,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134881446/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5712,6 +5758,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5721,12 +5768,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/30/2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5755,21 +5802,21 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>314349</v>
+        <v>0</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>306405692</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>11.300%</t>
+          <t>85.700%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>-28.700%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5779,7 +5826,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>PRGS-134191751</t>
+          <t>GECC-134881704</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5789,12 +5836,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134881704/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5812,6 +5859,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5821,12 +5869,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>03/12/2024</t>
+          <t>04/30/2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>General Insurance Company of America</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5836,40 +5884,40 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>8.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>14.000%</t>
+          <t>65.900%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>4.000%</t>
+          <t>-30.700%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5879,7 +5927,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>LBPM-133779020</t>
+          <t>GECC-134881704</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5889,12 +5937,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134881704/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5904,14 +5952,15 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5921,12 +5970,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>03/12/2024</t>
+          <t>04/30/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5936,40 +5985,40 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>8.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>76044</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>505</v>
+        <v>0</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>913384</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>34.000%</t>
+          <t>44.100%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2.000%</t>
+          <t>-27.400%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5979,7 +6028,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>LBPM-133779020</t>
+          <t>GECC-134881704</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5989,12 +6038,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134881704/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -6004,14 +6053,15 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6021,55 +6071,55 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>03/12/2024</t>
+          <t>03/01/2024</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>8.700%</t>
+          <t>27.500%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>8.000%</t>
+          <t>23.900%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>7848312</t>
+          <t>3820239</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>45298</v>
+        <v>9954</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>98199451</t>
+          <t>15970300</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>34.000%</t>
+          <t>46.200%</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.200%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6079,7 +6129,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>LBPM-133779020</t>
+          <t>LBPM-133883711</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -6089,12 +6139,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133883711/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -6112,6 +6162,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6121,55 +6172,55 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>06/19/2024</t>
+          <t>05/26/2024</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>12.600%</t>
+          <t>16.300%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>12.600%</t>
+          <t>6.400%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1219491</t>
+          <t>1119411</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>22355</v>
+        <v>10384</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>9701188</t>
+          <t>17592601</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>25.700%</t>
+          <t>29.769%</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.200%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6179,7 +6230,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>LBPM-133864197</t>
+          <t>LBPM-133977065</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -6189,12 +6240,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133864197/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133977065/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -6212,6 +6263,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6221,55 +6273,55 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>01/09/2024</t>
+          <t>04/26/2024</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>25.800%</t>
+          <t>12.800%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>15.200%</t>
+          <t>12.000%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>54501941</t>
+          <t>22813593</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>215944</v>
+        <v>133404</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>357929733</t>
+          <t>190113279</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>58.700%</t>
+          <t>21.000%</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6279,7 +6331,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>LBPM-133864423</t>
+          <t>PRGS-133899969</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -6289,12 +6341,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133864423/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133899969/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -6312,6 +6364,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6321,55 +6374,55 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>04/27/2024</t>
+          <t>04/26/2024</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>17.000%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>14.600%</t>
+          <t>10.600%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>63341742</t>
+          <t>29992321</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>260540</v>
+        <v>300545</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>434561908</t>
+          <t>282946429</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>39.600%</t>
+          <t>21.700%</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-9.100%</t>
+          <t>3.300%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6379,7 +6432,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>LBPM-133979163</t>
+          <t>PRGS-133899969</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6389,12 +6442,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133979163/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133899969/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6412,6 +6465,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6421,12 +6475,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>09/22/2024</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>General Insurance Company of America</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -6436,40 +6490,40 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>16.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>18.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7</v>
+        <v>136399</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>202923596</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>24.400%</t>
+          <t>8.800%</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>15.500%</t>
+          <t>-8.200%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6479,7 +6533,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>LBPM-134049356</t>
+          <t>PRGS-134191751</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6489,12 +6543,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -6504,14 +6558,15 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6521,12 +6576,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>09/22/2024</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6536,40 +6591,40 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>16.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>17.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>160434</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>486</v>
+        <v>314349</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>939400</t>
+          <t>306405692</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>31.700%</t>
+          <t>11.300%</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6579,7 +6634,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>LBPM-134049356</t>
+          <t>PRGS-134191751</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6589,12 +6644,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6604,14 +6659,15 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6621,12 +6677,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>09/22/2024</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6636,40 +6692,40 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>16.200%</t>
+          <t>3.800%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>16.000%</t>
+          <t>2.400%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>16499437</t>
+          <t>5712523</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>43948</v>
+        <v>155683</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>103370288</t>
+          <t>238021812</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>33.100%</t>
+          <t>28.900%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-26.500%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6679,7 +6735,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>LBPM-134049356</t>
+          <t>PRGS-134536924</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6689,12 +6745,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134536924/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -6704,14 +6760,15 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6721,12 +6778,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>09/22/2024</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Oregon</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6736,40 +6793,40 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>22.300%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>22.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2162665</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4597</v>
+        <v>414816</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>9794277</t>
+          <t>430306197</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>37.000%</t>
+          <t>47.600%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-24.500%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6779,7 +6836,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>LBPM-134066961</t>
+          <t>PRGS-134536924</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6789,12 +6846,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134066961/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134536924/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6804,14 +6861,15 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6821,12 +6879,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>03/16/2025</t>
+          <t>03/12/2024</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>General Insurance Company of America</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6836,40 +6894,40 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10.200%</t>
+          <t>8.700%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>986227</t>
+          <t>812</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>21127</v>
+        <v>8</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>9923754</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>14.000%</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.000%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6879,7 +6937,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>LBPM-134220016</t>
+          <t>LBPM-133779020</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6889,12 +6947,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134220016/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6904,14 +6962,15 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6921,7 +6980,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12/31/2025</t>
+          <t>03/12/2024</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6931,45 +6990,45 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>18.800%</t>
+          <t>8.700%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4.900%</t>
+          <t>8.300%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>563934</t>
+          <t>76044</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>11751</v>
+        <v>505</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>11487151</t>
+          <t>913384</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>6.800%</t>
+          <t>34.000%</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>2.000%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6979,7 +7038,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>LBPM-134619371</t>
+          <t>LBPM-133779020</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6989,12 +7048,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -7004,14 +7063,15 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7021,55 +7081,55 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>03/12/2024</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-3.100%</t>
+          <t>8.700%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>8.000%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-273240</t>
+          <t>7848312</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>36921</v>
+        <v>45298</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>8303864</t>
+          <t>98199451</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>34.000%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-37.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7079,7 +7139,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>LBPM-134745236</t>
+          <t>LBPM-133779020</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -7089,12 +7149,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -7104,14 +7164,15 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7121,40 +7182,55 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>02/01/2024</t>
+          <t>06/19/2024</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>12.600%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>12.600%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>62226</t>
+          <t>1219491</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>17675</v>
+        <v>22355</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>13517575</t>
+          <t>9701188</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>25.700%</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7164,7 +7240,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>SFMA-133686505</t>
+          <t>LBPM-133864197</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -7174,12 +7250,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133686505/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133864197/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -7197,6 +7273,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7206,55 +7283,55 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01/08/2024</t>
+          <t>01/09/2024</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>34.400%</t>
+          <t>25.800%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>17.100%</t>
+          <t>15.200%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>23629247</t>
+          <t>54501941</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>75857</v>
+        <v>215944</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>137915446</t>
+          <t>357929733</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>63.200%</t>
+          <t>58.700%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-3.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7264,7 +7341,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>SFMA-133737144</t>
+          <t>LBPM-133864423</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -7274,12 +7351,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133737144/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133864423/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -7297,6 +7374,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7306,55 +7384,55 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>01/08/2024</t>
+          <t>04/27/2024</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>18.000%</t>
+          <t>17.000%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>15.600%</t>
+          <t>14.600%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>171989837</t>
+          <t>63341742</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1193339</v>
+        <v>260540</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>1103919578</t>
+          <t>434561908</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>40.000%</t>
+          <t>39.600%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-5.400%</t>
+          <t>-9.100%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7364,7 +7442,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>SFMA-133737144</t>
+          <t>LBPM-133979163</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7374,12 +7452,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133737144/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133979163/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -7397,6 +7475,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7406,12 +7485,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>06/10/2024</t>
+          <t>09/22/2024</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>General Insurance Company of America</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7426,25 +7505,35 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>32.800%</t>
+          <t>16.200%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>14.500%</t>
+          <t>18.400%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>25053420</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>81718</v>
+        <v>7</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>172527324</t>
+          <t>12289</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>24.400%</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>15.500%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7454,7 +7543,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>SFMA-133957681</t>
+          <t>LBPM-134049356</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7464,12 +7553,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133957681/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -7487,6 +7576,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7496,12 +7586,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>06/10/2024</t>
+          <t>09/22/2024</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7516,25 +7606,35 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>16.600%</t>
+          <t>16.200%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>13.800%</t>
+          <t>17.100%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>175723240</t>
+          <t>160434</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1197563</v>
+        <v>486</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>1275343795</t>
+          <t>939400</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>31.700%</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>9.900%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7544,7 +7644,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>SFMA-133957681</t>
+          <t>LBPM-134049356</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7554,12 +7654,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133957681/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -7577,6 +7677,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7586,45 +7687,50 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>07/15/2024</t>
+          <t>09/22/2024</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>16.200%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>17.900%</t>
+          <t>16.000%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>69353041</t>
+          <t>16499437</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>525150</v>
+        <v>43948</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>387128333</t>
+          <t>103370288</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>31.200%</t>
+          <t>33.100%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7639,7 +7745,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>SFMA-134044384</t>
+          <t>LBPM-134049356</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7649,12 +7755,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134044384/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -7672,6 +7778,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7681,12 +7788,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>08/01/2024</t>
+          <t>09/22/2024</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Oregon</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -7696,40 +7803,40 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>22.300%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>22.100%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2162665</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>2020</v>
+        <v>4597</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>1139756</t>
+          <t>9794277</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>37.000%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-9.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7739,7 +7846,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>SFMA-134076828</t>
+          <t>LBPM-134066961</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7749,12 +7856,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134076828/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134066961/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7772,6 +7879,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7781,12 +7889,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>08/01/2024</t>
+          <t>03/16/2025</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7801,35 +7909,35 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.200%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.900%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>986227</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>33343</v>
+        <v>21127</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>9698904</t>
+          <t>9923754</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>9.500%</t>
+          <t>13.700%</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-9.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7839,7 +7947,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>SFMA-134076828</t>
+          <t>LBPM-134220016</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7849,12 +7957,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134076828/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134220016/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -7864,14 +7972,15 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
-        </is>
-      </c>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7881,12 +7990,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>12/31/2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -7896,35 +8005,40 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>04.0001 Condominium Homeowners</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>18.800%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>21.500%</t>
+          <t>4.900%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>10650679</t>
+          <t>563934</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>59070</v>
+        <v>11751</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>49543045</t>
+          <t>11487151</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>22.800%</t>
+          <t>6.800%</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -7934,7 +8048,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>SFMA-134315085</t>
+          <t>LBPM-134619371</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -7944,12 +8058,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134315085/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -7967,6 +8081,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -7976,12 +8091,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>04/15/2026</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -7991,35 +8106,40 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-3.100%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>93.700%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2706726</t>
+          <t>-273240</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>8405</v>
+        <v>36921</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2888541</t>
+          <t>8303864</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>108.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>31.400%</t>
+          <t>-37.500%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8029,7 +8149,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>SFMA-134315091</t>
+          <t>LBPM-134745236</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -8039,12 +8159,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134315091/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -8062,6 +8182,7 @@
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8071,7 +8192,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>08/01/2025</t>
+          <t>02/01/2024</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8091,30 +8212,20 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>23.900%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>3367834</t>
+          <t>62226</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>17873</v>
+        <v>17675</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>14091908</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>27.700%</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>5.100%</t>
+          <t>13517575</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8124,7 +8235,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>SFMA-134422784</t>
+          <t>SFMA-133686505</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -8134,12 +8245,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134422784/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133686505/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -8149,14 +8260,15 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8166,12 +8278,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>02/25/2024</t>
+          <t>01/08/2024</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8181,35 +8293,40 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>34.400%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>17.100%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23629247</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>3955</v>
+        <v>75857</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>7784317</t>
+          <t>137915446</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>63.200%</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.800%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8219,7 +8336,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>TRVD-133853983</t>
+          <t>SFMA-133737144</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -8229,12 +8346,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133853983/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133737144/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -8252,6 +8369,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8261,12 +8379,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>02/25/2024</t>
+          <t>01/08/2024</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -8276,35 +8394,40 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>18.000%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.600%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>171989837</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>783</v>
+        <v>1193339</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>1381984</t>
+          <t>1103919578</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>40.000%</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-5.400%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -8314,7 +8437,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>TRVD-133853983</t>
+          <t>SFMA-133737144</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -8324,12 +8447,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133853983/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133737144/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -8347,6 +8470,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8356,55 +8480,45 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>05/03/2025</t>
+          <t>06/10/2024</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>41.800%</t>
+          <t>32.800%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>33.500%</t>
+          <t>14.500%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>25053420</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>163</v>
+        <v>81718</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>42058</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>59.400%</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>13.300%</t>
+          <t>172527324</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -8414,7 +8528,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>TRVD-134151094</t>
+          <t>SFMA-133957681</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -8422,9 +8536,14 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2024-02-02</t>
+        </is>
+      </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134151094/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133957681/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -8439,9 +8558,10 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8451,55 +8571,45 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>12/13/2024</t>
+          <t>06/10/2024</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>36.100%</t>
+          <t>16.600%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>21.600%</t>
+          <t>13.800%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>20285484</t>
+          <t>175723240</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>74773</v>
+        <v>1197563</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>93914279</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>64.300%</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>0.000%</t>
+          <t>1275343795</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8509,7 +8619,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>TRVD-G134214259</t>
+          <t>SFMA-133957681</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -8519,12 +8629,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134220061/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133957681/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -8542,6 +8652,7 @@
           <t>pipeline_extracted</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8551,12 +8662,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>02/08/2025</t>
+          <t>07/15/2024</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -8569,32 +8680,27 @@
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>31.500%</t>
-        </is>
-      </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>21.100%</t>
+          <t>17.900%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>10657508</t>
+          <t>69353041</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>39456</v>
+        <v>525150</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>50509518</t>
+          <t>387128333</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>33.400%</t>
+          <t>31.200%</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8609,7 +8715,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>TRVD-G134262689</t>
+          <t>SFMA-134044384</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8619,12 +8725,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134044384/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -8634,14 +8740,15 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8651,55 +8758,55 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>02/08/2025</t>
+          <t>08/01/2024</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>31.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>21.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>636936</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2461</v>
+        <v>2020</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2976338</t>
+          <t>1139756</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>32.600%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-9.500%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8709,7 +8816,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>TRVD-G134262689</t>
+          <t>SFMA-134076828</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8719,12 +8826,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134076828/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -8734,14 +8841,15 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8751,12 +8859,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>03/30/2025</t>
+          <t>08/01/2024</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -8766,7 +8874,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8785,21 +8893,21 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>2483</v>
+        <v>33343</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>4953073</t>
+          <t>9698904</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.500%</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-9.000%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8809,7 +8917,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>TRVD-G134336116</t>
+          <t>SFMA-134076828</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8819,12 +8927,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134358134/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134076828/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -8834,14 +8942,15 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8851,92 +8960,1270 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
+          <t>12/15/2025</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>21.500%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>10650679</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>59070</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>49543045</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>22.800%</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>SFMA-134315085</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134315085/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>04/15/2026</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>04.0005 Other Homeowners</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>93.700%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2706726</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>8405</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2888541</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>108.400%</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>31.400%</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>SFMA-134315091</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134315091/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>08/01/2025</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>04.0002 Mobile Homeowners</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>23.900%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>3367834</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>17873</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>14091908</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>27.700%</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>5.100%</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>SFMA-134422784</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134422784/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>12/15/2023</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>8.700%</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>8.500%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>5917059</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>60469</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>69612453</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>30.300%</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>TRVD-133781000</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133781000/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>02/25/2024</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>3955</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>7784317</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>TRVD-133853983</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133853983/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>02/25/2024</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>783</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>1381984</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>TRVD-133853983</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2023-11-02</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/133853983/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>05/03/2025</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>41.800%</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>33.500%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>163</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>59.400%</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>13.300%</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>TRVD-134151094</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134151094/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>12/13/2024</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>36.100%</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>21.600%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>20285484</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>74773</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>93914279</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>64.300%</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>TRVD-G134214259</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134220061/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>02/08/2025</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>31.500%</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>21.100%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>10657508</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>39456</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>50509518</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>33.400%</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>TRVD-G134262689</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>02/08/2025</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>31.500%</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>21.400%</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>636936</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>2461</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2976338</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>32.600%</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>TRVD-G134262689</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>03/30/2025</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>2483</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>4953073</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>TRVD-G134336116</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134358134/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>03/30/2025</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
         <is>
           <t>Travelers Commercial Insurance Company</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>19.0 Personal Auto</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I86" t="n">
+      <c r="I97" t="n">
         <v>495</v>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>910721</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>TRVD-G134336116</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="P97" t="inlineStr">
         <is>
           <t>2024-12-19</t>
         </is>
       </c>
-      <c r="Q86" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>output/pdfs/WA/134358134/filing_summary.pdf</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="R97" t="inlineStr">
         <is>
           <t>pipeline_only</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr">
+      <c r="S97" t="inlineStr">
         <is>
           <t>original</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr">
+      <c r="T97" t="inlineStr">
         <is>
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>05/09/2026</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>20.700%</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>20.500%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>11296</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>170</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>55100</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>28.300%</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>10.600%</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>TRVD-G134707053</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134712767/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/wa_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U98"/>
+  <dimension ref="A1:U106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4152,12 +4152,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>07/18/2024</t>
+          <t>05/18/2024</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4186,21 +4186,21 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>18641</v>
+        <v>30</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>10082975</t>
+          <t>310535413</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>65.900%</t>
+          <t>22.500%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-53.960%</t>
+          <t>-22.800%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>GECC-134044540</t>
+          <t>GECC-133752316</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2024-04-01</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134044540/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133752316/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>05/18/2024</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4287,21 +4287,21 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>42889</v>
+        <v>15</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>83538733</t>
+          <t>139896774</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>126.400%</t>
+          <t>17.100%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-39.700%</t>
+          <t>-13.800%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>GECC-134126215</t>
+          <t>GECC-133752316</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -4321,12 +4321,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134126215/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133752316/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>05/18/2024</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4388,21 +4388,21 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>12607</v>
+        <v>7</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>25367953</t>
+          <t>71886332</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>126.500%</t>
+          <t>12.200%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-20.400%</t>
+          <t>-13.200%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>GECC-134126215</t>
+          <t>GECC-133752316</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134126215/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133752316/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10/10/2024</t>
+          <t>07/18/2024</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4489,21 +4489,21 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>10898</v>
+        <v>18641</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>29466421</t>
+          <t>10082975</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>41.300%</t>
+          <t>65.900%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-23.900%</t>
+          <t>-53.960%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>GECC-134126294</t>
+          <t>GECC-134044540</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2024-05-31</t>
+          <t>2024-04-01</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134126294/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134044540/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4590,21 +4590,21 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>182963</v>
+        <v>42889</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>340981796</t>
+          <t>83538733</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>126.600%</t>
+          <t>126.400%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-43.700%</t>
+          <t>-39.700%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>GECC-134126318</t>
+          <t>GECC-134126215</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134126215/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4691,21 +4691,21 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>70409</v>
+        <v>12607</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>162085401</t>
+          <t>25367953</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>122.200%</t>
+          <t>126.500%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-40.600%</t>
+          <t>-20.400%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>GECC-134126318</t>
+          <t>GECC-134126215</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134126215/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4763,7 +4763,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4792,21 +4792,21 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>24488</v>
+        <v>10898</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>73529867</t>
+          <t>29466421</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>146.400%</t>
+          <t>41.300%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-45.400%</t>
+          <t>-23.900%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>GECC-134126318</t>
+          <t>GECC-134126294</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134126294/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4893,21 +4893,21 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2090</v>
+        <v>182963</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1077172</t>
+          <t>340981796</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>24.800%</t>
+          <t>126.600%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-17.900%</t>
+          <t>-43.700%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4917,7 +4917,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>GECC-134628136</t>
+          <t>GECC-134126318</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -4942,12 +4942,12 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U45" t="inlineStr"/>
@@ -4960,12 +4960,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4975,7 +4975,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4994,21 +4994,21 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>946</v>
+        <v>70409</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>493777</t>
+          <t>162085401</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>24.400%</t>
+          <t>122.200%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-17.500%</t>
+          <t>-40.600%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>GECC-134628136</t>
+          <t>GECC-134126318</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -5028,12 +5028,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -5043,12 +5043,12 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U46" t="inlineStr"/>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>09/18/2025</t>
+          <t>10/10/2024</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5095,21 +5095,21 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>468</v>
+        <v>24488</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>313322</t>
+          <t>73529867</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>22.000%</t>
+          <t>146.400%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-15.200%</t>
+          <t>-45.400%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>GECC-134629877</t>
+          <t>GECC-134126318</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2024-05-31</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629877/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134126318/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U47" t="inlineStr"/>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5196,21 +5196,21 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6838</v>
+        <v>2090</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>3570611</t>
+          <t>1077172</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>22.700%</t>
+          <t>24.800%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-18.900%</t>
+          <t>-17.900%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>GECC-134629950</t>
+          <t>GECC-134628136</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1090</v>
+        <v>946</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>851643</t>
+          <t>493777</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>22.200%</t>
+          <t>24.400%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-19.000%</t>
+          <t>-17.500%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>GECC-134629950</t>
+          <t>GECC-134628136</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134628136/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -5369,7 +5369,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -5398,21 +5398,21 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>220</v>
+        <v>468</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>268980</t>
+          <t>313322</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>19.400%</t>
+          <t>22.000%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-15.800%</t>
+          <t>-15.200%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5422,7 +5422,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>GECC-134629950</t>
+          <t>GECC-134629877</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134629877/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>04/30/2026</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5499,21 +5499,21 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>6838</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3570611</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>59.800%</t>
+          <t>22.700%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-24.600%</t>
+          <t>-18.900%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>GECC-134879681</t>
+          <t>GECC-134629950</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -5533,12 +5533,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134879681/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>04/30/2026</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5600,21 +5600,21 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>1090</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>851643</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>44.800%</t>
+          <t>22.200%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-25.000%</t>
+          <t>-19.000%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>GECC-134879681</t>
+          <t>GECC-134629950</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134879681/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>04/30/2026</t>
+          <t>09/18/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5701,21 +5701,21 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>268980</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>35.300%</t>
+          <t>19.400%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>-15.500%</t>
+          <t>-15.800%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>GECC-134881446</t>
+          <t>GECC-134629950</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -5735,12 +5735,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134881446/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134629950/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GEICO Advantage Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>85.700%</t>
+          <t>59.800%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-28.700%</t>
+          <t>-24.600%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>GECC-134881704</t>
+          <t>GECC-134879681</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134881704/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134879681/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>65.900%</t>
+          <t>44.800%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-30.700%</t>
+          <t>-25.000%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>GECC-134881704</t>
+          <t>GECC-134879681</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134881704/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134879681/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>44.100%</t>
+          <t>35.300%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-27.400%</t>
+          <t>-15.500%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>GECC-134881704</t>
+          <t>GECC-134881446</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134881704/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134881446/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -6071,55 +6071,55 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>03/01/2024</t>
+          <t>04/30/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>GEICO Advantage Insurance Company</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>27.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>23.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3820239</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>9954</v>
+        <v>0</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>15970300</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>46.200%</t>
+          <t>85.700%</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2.200%</t>
+          <t>-28.700%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>LBPM-133883711</t>
+          <t>GECC-134881704</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133883711/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134881704/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U57" t="inlineStr"/>
@@ -6172,55 +6172,55 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>05/26/2024</t>
+          <t>04/30/2026</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>16.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>6.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1119411</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>10384</v>
+        <v>0</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>17592601</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>29.769%</t>
+          <t>65.900%</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2.200%</t>
+          <t>-30.700%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>LBPM-133977065</t>
+          <t>GECC-134881704</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2024-02-01</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133977065/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134881704/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U58" t="inlineStr"/>
@@ -6273,12 +6273,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>04/26/2024</t>
+          <t>04/30/2026</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -6293,35 +6293,35 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>12.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>12.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>22813593</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>133404</v>
+        <v>0</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>190113279</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>21.000%</t>
+          <t>44.100%</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>-27.400%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>PRGS-133899969</t>
+          <t>GECC-134881704</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133899969/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134881704/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U59" t="inlineStr"/>
@@ -6374,55 +6374,55 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>04/26/2024</t>
+          <t>03/01/2024</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>12.500%</t>
+          <t>27.500%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>10.600%</t>
+          <t>23.900%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>29992321</t>
+          <t>3820239</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>300545</v>
+        <v>9954</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>282946429</t>
+          <t>15970300</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>21.700%</t>
+          <t>46.200%</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>3.300%</t>
+          <t>2.200%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>PRGS-133899969</t>
+          <t>LBPM-133883711</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>2023-11-10</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133899969/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133883711/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -6475,55 +6475,55 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>05/26/2024</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>16.300%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.400%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1119411</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>136399</v>
+        <v>10384</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>202923596</t>
+          <t>17592601</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8.800%</t>
+          <t>29.769%</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-8.200%</t>
+          <t>2.200%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -6533,7 +6533,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>PRGS-134191751</t>
+          <t>LBPM-133977065</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2024-02-01</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133977065/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -6558,12 +6558,12 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U61" t="inlineStr"/>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>02/07/2025</t>
+          <t>04/26/2024</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -6596,35 +6596,35 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.800%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.000%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22813593</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>314349</v>
+        <v>133404</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>306405692</t>
+          <t>190113279</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>11.300%</t>
+          <t>21.000%</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6634,7 +6634,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>PRGS-134191751</t>
+          <t>PRGS-133899969</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133899969/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U62" t="inlineStr"/>
@@ -6677,12 +6677,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>04/26/2024</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -6697,35 +6697,35 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>3.800%</t>
+          <t>12.500%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2.400%</t>
+          <t>10.600%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>5712523</t>
+          <t>29992321</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>155683</v>
+        <v>300545</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>238021812</t>
+          <t>282946429</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>28.900%</t>
+          <t>21.700%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-26.500%</t>
+          <t>3.300%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>PRGS-134536924</t>
+          <t>PRGS-133899969</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -6745,12 +6745,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2023-11-28</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134536924/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133899969/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U63" t="inlineStr"/>
@@ -6778,12 +6778,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>03/07/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -6793,40 +6793,40 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>13.000%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.400%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2323100</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>414816</v>
+        <v>60416</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>430306197</t>
+          <t>21922909</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>47.600%</t>
+          <t>317.400%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-24.500%</t>
+          <t>-66.000%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>PRGS-134536924</t>
+          <t>PRGS-133964756</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2024-02-21</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134536924/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133964756/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>03/12/2024</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>General Insurance Company of America</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -6894,40 +6894,40 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>8.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8</v>
+        <v>136399</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>202923596</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>14.000%</t>
+          <t>8.800%</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>4.000%</t>
+          <t>-8.200%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>LBPM-133779020</t>
+          <t>PRGS-134191751</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U65" t="inlineStr"/>
@@ -6980,12 +6980,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>03/12/2024</t>
+          <t>02/07/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6995,40 +6995,40 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>8.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>8.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>76044</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>505</v>
+        <v>314349</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>913384</t>
+          <t>306405692</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>34.000%</t>
+          <t>11.300%</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>2.000%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>LBPM-133779020</t>
+          <t>PRGS-134191751</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134191751/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -7063,12 +7063,12 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U66" t="inlineStr"/>
@@ -7081,12 +7081,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>03/12/2024</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -7096,40 +7096,40 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>8.700%</t>
+          <t>3.800%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>8.000%</t>
+          <t>2.400%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>7848312</t>
+          <t>5712523</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>45298</v>
+        <v>155683</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>98199451</t>
+          <t>238021812</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>34.000%</t>
+          <t>28.900%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-26.500%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -7139,7 +7139,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>LBPM-133779020</t>
+          <t>PRGS-134536924</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134536924/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U67" t="inlineStr"/>
@@ -7182,12 +7182,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>06/19/2024</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -7197,40 +7197,40 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>12.600%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>12.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1219491</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>22355</v>
+        <v>414816</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>9701188</t>
+          <t>430306197</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>25.700%</t>
+          <t>47.600%</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-24.500%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>LBPM-133864197</t>
+          <t>PRGS-134536924</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133864197/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134536924/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U68" t="inlineStr"/>
@@ -7283,55 +7283,55 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>01/09/2024</t>
+          <t>03/12/2024</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>General Insurance Company of America</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>25.800%</t>
+          <t>8.700%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>15.200%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>54501941</t>
+          <t>812</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>215944</v>
+        <v>8</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>357929733</t>
+          <t>11561</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>58.700%</t>
+          <t>14.000%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.000%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>LBPM-133864423</t>
+          <t>LBPM-133779020</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133864423/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -7384,7 +7384,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>04/27/2024</t>
+          <t>03/12/2024</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -7394,45 +7394,45 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>17.000%</t>
+          <t>8.700%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>14.600%</t>
+          <t>8.300%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>63341742</t>
+          <t>76044</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>260540</v>
+        <v>505</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>434561908</t>
+          <t>913384</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>39.600%</t>
+          <t>34.000%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-9.100%</t>
+          <t>2.000%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>LBPM-133979163</t>
+          <t>LBPM-133779020</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2024-02-05</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133979163/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>09/22/2024</t>
+          <t>03/12/2024</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>General Insurance Company of America</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -7505,35 +7505,35 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>16.200%</t>
+          <t>8.700%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>18.400%</t>
+          <t>8.000%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>7848312</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>45298</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>98199451</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>24.400%</t>
+          <t>34.000%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>15.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>LBPM-134049356</t>
+          <t>LBPM-133779020</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -7553,12 +7553,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2023-08-14</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133779020/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>09/22/2024</t>
+          <t>06/19/2024</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -7601,40 +7601,40 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>16.200%</t>
+          <t>12.600%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>17.100%</t>
+          <t>12.600%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>160434</t>
+          <t>1219491</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>486</v>
+        <v>22355</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>939400</t>
+          <t>9701188</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>31.700%</t>
+          <t>25.700%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>LBPM-134049356</t>
+          <t>LBPM-133864197</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133864197/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -7687,50 +7687,50 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>09/22/2024</t>
+          <t>01/09/2024</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>16.200%</t>
+          <t>25.800%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>16.000%</t>
+          <t>15.200%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>16499437</t>
+          <t>54501941</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>43948</v>
+        <v>215944</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>103370288</t>
+          <t>357929733</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>33.100%</t>
+          <t>58.700%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>LBPM-134049356</t>
+          <t>LBPM-133864423</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2024-03-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133864423/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -7788,55 +7788,55 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>09/22/2024</t>
+          <t>04/27/2024</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Oregon</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>22.300%</t>
+          <t>17.000%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>22.100%</t>
+          <t>14.600%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2162665</t>
+          <t>63341742</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4597</v>
+        <v>260540</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>9794277</t>
+          <t>434561908</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>37.000%</t>
+          <t>39.600%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-9.100%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>LBPM-134066961</t>
+          <t>LBPM-133979163</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2024-04-16</t>
+          <t>2024-02-05</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134066961/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133979163/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -7889,12 +7889,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>03/16/2025</t>
+          <t>09/22/2024</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of Illinois</t>
+          <t>General Insurance Company of America</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -7904,40 +7904,40 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>10.200%</t>
+          <t>16.200%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>18.400%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>986227</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>21127</v>
+        <v>7</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>9923754</t>
+          <t>12289</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>13.700%</t>
+          <t>24.400%</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.500%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>LBPM-134220016</t>
+          <t>LBPM-134049356</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2024-08-22</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134220016/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U75" t="inlineStr"/>
@@ -7990,7 +7990,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12/31/2025</t>
+          <t>09/22/2024</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8000,45 +8000,45 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>18.800%</t>
+          <t>16.200%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>4.900%</t>
+          <t>17.100%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>563934</t>
+          <t>160434</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>11751</v>
+        <v>486</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>11487151</t>
+          <t>939400</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>6.800%</t>
+          <t>31.700%</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>9.900%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>LBPM-134619371</t>
+          <t>LBPM-134049356</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -8058,12 +8058,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -8073,12 +8073,12 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U76" t="inlineStr"/>
@@ -8091,55 +8091,55 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>02/21/2026</t>
+          <t>09/22/2024</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>-3.100%</t>
+          <t>16.200%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>16.000%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-273240</t>
+          <t>16499437</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>36921</v>
+        <v>43948</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>8303864</t>
+          <t>103370288</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>33.100%</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-37.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>LBPM-134745236</t>
+          <t>LBPM-134049356</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -8159,12 +8159,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2024-03-29</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134049356/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -8174,12 +8174,12 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U77" t="inlineStr"/>
@@ -8192,40 +8192,55 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>02/01/2024</t>
+          <t>09/22/2024</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Oregon</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>22.300%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>22.100%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>62226</t>
+          <t>2162665</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>17675</v>
+        <v>4597</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>13517575</t>
+          <t>9794277</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>37.000%</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -8235,7 +8250,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>SFMA-133686505</t>
+          <t>LBPM-134066961</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -8245,12 +8260,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2023-07-05</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133686505/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134066961/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -8278,12 +8293,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01/08/2024</t>
+          <t>03/16/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of Illinois</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -8293,40 +8308,40 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>34.400%</t>
+          <t>10.200%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>17.100%</t>
+          <t>9.900%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>23629247</t>
+          <t>986227</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>75857</v>
+        <v>21127</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>137915446</t>
+          <t>9923754</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>63.200%</t>
+          <t>13.700%</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-3.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8336,7 +8351,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>SFMA-133737144</t>
+          <t>LBPM-134220016</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -8346,12 +8361,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2024-08-22</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133737144/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134220016/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -8361,12 +8376,12 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U79" t="inlineStr"/>
@@ -8379,55 +8394,55 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>01/08/2024</t>
+          <t>12/31/2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>18.000%</t>
+          <t>18.800%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>15.600%</t>
+          <t>4.900%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>171989837</t>
+          <t>563934</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1193339</v>
+        <v>11751</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>1103919578</t>
+          <t>11487151</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>40.000%</t>
+          <t>6.800%</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-5.400%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -8437,7 +8452,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>SFMA-133737144</t>
+          <t>LBPM-134619371</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -8447,12 +8462,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2023-07-21</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133737144/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134619371/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -8462,12 +8477,12 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U80" t="inlineStr"/>
@@ -8480,45 +8495,55 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>06/10/2024</t>
+          <t>02/21/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>32.800%</t>
+          <t>-3.100%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>14.500%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>25053420</t>
+          <t>-273240</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>81718</v>
+        <v>36921</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>172527324</t>
+          <t>8303864</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>-37.500%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -8528,7 +8553,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>SFMA-133957681</t>
+          <t>LBPM-134745236</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -8538,12 +8563,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133957681/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134745236/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -8553,12 +8578,12 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U81" t="inlineStr"/>
@@ -8571,45 +8596,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>06/10/2024</t>
+          <t>02/01/2024</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>16.600%</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>13.800%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>175723240</t>
+          <t>62226</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1197563</v>
+        <v>17675</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>1275343795</t>
+          <t>13517575</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -8619,7 +8639,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>SFMA-133957681</t>
+          <t>SFMA-133686505</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -8629,12 +8649,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2023-07-05</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133957681/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133686505/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -8662,7 +8682,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>07/15/2024</t>
+          <t>01/08/2024</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8672,40 +8692,45 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>34.400%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>17.900%</t>
+          <t>17.100%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>69353041</t>
+          <t>23629247</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>525150</v>
+        <v>75857</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>387128333</t>
+          <t>137915446</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>31.200%</t>
+          <t>63.200%</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.800%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -8715,7 +8740,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>SFMA-134044384</t>
+          <t>SFMA-133737144</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -8725,12 +8750,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134044384/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133737144/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -8758,12 +8783,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>08/01/2024</t>
+          <t>01/08/2024</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -8773,40 +8798,40 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>18.000%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.600%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>171989837</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2020</v>
+        <v>1193339</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>1139756</t>
+          <t>1103919578</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>40.000%</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-9.500%</t>
+          <t>-5.400%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -8816,7 +8841,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>SFMA-134076828</t>
+          <t>SFMA-133737144</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -8826,12 +8851,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2023-07-21</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134076828/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133737144/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -8859,12 +8884,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>08/01/2024</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -8874,7 +8899,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8893,21 +8918,21 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>33343</v>
+        <v>71073</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>9698904</t>
+          <t>99678958</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>9.500%</t>
+          <t>23.500%</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-9.000%</t>
+          <t>-24.000%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -8917,7 +8942,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>SFMA-134076828</t>
+          <t>SFMA-133804251</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -8927,12 +8952,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134076828/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133804251/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -8960,50 +8985,55 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>01/01/2024</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>21.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>10650679</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>59070</v>
+        <v>1072861</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>49543045</t>
+          <t>859226992</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>22.800%</t>
+          <t>20.800%</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-20.600%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -9013,7 +9043,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>SFMA-134315085</t>
+          <t>SFMA-133804251</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -9023,12 +9053,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2023-10-19</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134315085/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133804251/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -9038,12 +9068,12 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U86" t="inlineStr"/>
@@ -9056,7 +9086,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>04/15/2026</t>
+          <t>06/10/2024</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -9066,40 +9096,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>32.800%</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>93.700%</t>
+          <t>14.500%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2706726</t>
+          <t>25053420</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8405</v>
+        <v>81718</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2888541</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>108.400%</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>31.400%</t>
+          <t>172527324</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -9109,7 +9134,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>SFMA-134315091</t>
+          <t>SFMA-133957681</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -9119,12 +9144,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134315091/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133957681/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -9134,12 +9159,12 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U87" t="inlineStr"/>
@@ -9152,50 +9177,45 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>08/01/2025</t>
+          <t>06/10/2024</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>16.600%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>23.900%</t>
+          <t>13.800%</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>3367834</t>
+          <t>175723240</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>17873</v>
+        <v>1197563</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>14091908</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>27.700%</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>5.100%</t>
+          <t>1275343795</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9205,7 +9225,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>SFMA-134422784</t>
+          <t>SFMA-133957681</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -9215,12 +9235,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134422784/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133957681/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -9230,12 +9250,12 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U88" t="inlineStr"/>
@@ -9248,12 +9268,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>12/15/2023</t>
+          <t>07/15/2024</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -9266,32 +9286,27 @@
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>8.700%</t>
-        </is>
-      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>8.500%</t>
+          <t>17.900%</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>5917059</t>
+          <t>69353041</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>60469</v>
+        <v>525150</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>69612453</t>
+          <t>387128333</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>30.300%</t>
+          <t>31.200%</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -9306,7 +9321,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>TRVD-133781000</t>
+          <t>SFMA-134044384</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -9314,9 +9329,14 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133781000/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134044384/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -9344,12 +9364,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>02/25/2024</t>
+          <t>08/01/2024</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -9359,7 +9379,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9373,21 +9398,21 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>3955</v>
+        <v>2020</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>7784317</t>
+          <t>1139756</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-9.500%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9397,7 +9422,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>TRVD-133853983</t>
+          <t>SFMA-134076828</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -9407,12 +9432,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133853983/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134076828/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -9440,12 +9465,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>02/25/2024</t>
+          <t>08/01/2024</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -9455,7 +9480,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -9469,21 +9499,21 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>783</v>
+        <v>33343</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>1381984</t>
+          <t>9698904</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.500%</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-9.000%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9493,7 +9523,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>TRVD-133853983</t>
+          <t>SFMA-134076828</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -9503,12 +9533,12 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2023-11-02</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/133853983/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134076828/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -9536,12 +9566,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>05/03/2025</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -9551,40 +9581,35 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>41.800%</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>33.500%</t>
+          <t>21.500%</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>10650679</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>163</v>
+        <v>59070</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>42058</t>
+          <t>49543045</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>59.400%</t>
+          <t>22.800%</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>13.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -9594,7 +9619,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>TRVD-134151094</t>
+          <t>SFMA-134315085</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -9602,9 +9627,14 @@
           <t>Approved</t>
         </is>
       </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2024-11-27</t>
+        </is>
+      </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134151094/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134315085/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -9614,7 +9644,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T92" t="inlineStr">
@@ -9632,12 +9662,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>12/13/2024</t>
+          <t>04/15/2026</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -9647,40 +9677,35 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>36.100%</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>21.600%</t>
+          <t>93.700%</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>20285484</t>
+          <t>2706726</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>74773</v>
+        <v>8405</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>93914279</t>
+          <t>2888541</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>64.300%</t>
+          <t>108.400%</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>31.400%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -9690,7 +9715,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>TRVD-G134214259</t>
+          <t>SFMA-134315091</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -9700,12 +9725,12 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2024-08-20</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134220061/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134315091/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -9715,12 +9740,12 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>extension</t>
+          <t>original</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>pipeline_extracted</t>
+          <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
       <c r="U93" t="inlineStr"/>
@@ -9733,12 +9758,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>02/08/2025</t>
+          <t>08/01/2025</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -9748,40 +9773,35 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>31.500%</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>21.100%</t>
+          <t>23.900%</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>10657508</t>
+          <t>3367834</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>39456</v>
+        <v>17873</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>50509518</t>
+          <t>14091908</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>33.400%</t>
+          <t>27.700%</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>5.100%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -9791,7 +9811,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>TRVD-G134262689</t>
+          <t>SFMA-134422784</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -9801,12 +9821,12 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+          <t>output/pdfs/WA/134422784/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -9834,12 +9854,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>02/08/2025</t>
+          <t>12/15/2023</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -9854,30 +9874,30 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>31.500%</t>
+          <t>8.700%</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>21.400%</t>
+          <t>8.500%</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>636936</t>
+          <t>5917059</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>2461</v>
+        <v>60469</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2976338</t>
+          <t>69612453</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>32.600%</t>
+          <t>30.300%</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -9892,7 +9912,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>TRVD-G134262689</t>
+          <t>TRVD-133781000</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -9900,14 +9920,9 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
-        <is>
-          <t>2024-10-02</t>
-        </is>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133781000/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -9917,12 +9932,12 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U95" t="inlineStr"/>
@@ -9935,7 +9950,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>03/30/2025</t>
+          <t>02/25/2024</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -9953,11 +9968,6 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>0.000%</t>
@@ -9969,11 +9979,11 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2483</v>
+        <v>3955</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>4953073</t>
+          <t>7784317</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -9993,7 +10003,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>TRVD-G134336116</t>
+          <t>TRVD-133853983</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -10003,12 +10013,12 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134358134/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133853983/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -10018,12 +10028,12 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U96" t="inlineStr"/>
@@ -10036,7 +10046,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>03/30/2025</t>
+          <t>02/25/2024</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -10054,11 +10064,6 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
       <c r="G97" t="inlineStr">
         <is>
           <t>0.000%</t>
@@ -10070,11 +10075,11 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>495</v>
+        <v>783</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>910721</t>
+          <t>1381984</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -10082,6 +10087,11 @@
           <t>0.000%</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
           <t>rate_change</t>
@@ -10089,7 +10099,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>TRVD-G134336116</t>
+          <t>TRVD-133853983</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -10099,12 +10109,12 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>output/pdfs/WA/134358134/filing_summary.pdf</t>
+          <t>output/pdfs/WA/133853983/filing_summary.pdf</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -10114,12 +10124,12 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>original</t>
+          <t>extension</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>pipeline_extracted_in_validated_window</t>
+          <t>pipeline_extracted</t>
         </is>
       </c>
       <c r="U97" t="inlineStr"/>
@@ -10132,98 +10142,886 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
+          <t>05/03/2025</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>41.800%</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>33.500%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>163</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>59.400%</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>13.300%</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>TRVD-134151094</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134151094/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>12/13/2024</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>36.100%</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>21.600%</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>20285484</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>74773</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>93914279</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>64.300%</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>TRVD-G134214259</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134220061/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>02/08/2025</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>31.500%</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>21.100%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>10657508</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>39456</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>50509518</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>33.400%</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>TRVD-G134262689</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>02/08/2025</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>31.500%</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>21.400%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>636936</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>2461</v>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2976338</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>32.600%</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>TRVD-G134262689</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>2024-10-02</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134270699/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>03/30/2025</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>2483</v>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>4953073</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>TRVD-G134336116</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134358134/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>03/30/2025</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>495</v>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>910721</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>TRVD-G134336116</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134358134/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>05/09/2026</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>04.0 Homeowners</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>20.700%</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>20.500%</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>11296</t>
         </is>
       </c>
-      <c r="I98" t="n">
+      <c r="I104" t="n">
         <v>170</v>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>55100</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>28.300%</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>10.600%</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>rate_change</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t>TRVD-G134707053</t>
         </is>
       </c>
-      <c r="O98" t="inlineStr">
+      <c r="O104" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="P98" t="inlineStr">
+      <c r="P104" t="inlineStr">
         <is>
           <t>2025-10-22</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>output/pdfs/WA/134712767/filing_summary.pdf</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="R104" t="inlineStr">
         <is>
           <t>pipeline_only</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>original</t>
         </is>
       </c>
-      <c r="T98" t="inlineStr">
+      <c r="T104" t="inlineStr">
         <is>
           <t>pipeline_extracted_in_validated_window</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>07/20/2026</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>498300274</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>ALSE-134915392</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134915392/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>07/20/2026</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Allstate Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>6820340</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>ALSE-134915159</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>output/pdfs/WA/134915159/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
